--- a/input/Spinning.xlsx
+++ b/input/Spinning.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikhitha\OneDrive\Desktop\Manning_AUM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://welspungroup-my.sharepoint.com/personal/sahith_thadimudupula_welspun_com/Documents/Desktop/Manning_FInal_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27A5A94-B1FD-49F2-9F70-8465DE6A863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{A27A5A94-B1FD-49F2-9F70-8465DE6A863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E476F20-40BC-4B9D-8573-7B5DC7559817}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spinning" sheetId="1" r:id="rId1"/>
     <sheet name="TFO" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spinning!$A$1:$T$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spinning!$A$1:$U$117</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="287">
   <si>
     <t>Location</t>
   </si>
@@ -893,6 +893,9 @@
   </si>
   <si>
     <t>Dept_Machine_Name</t>
+  </si>
+  <si>
+    <t>Manpower_Base_Qty</t>
   </si>
 </sst>
 </file>
@@ -956,36 +959,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="32">
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1354,6 +1346,36 @@
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1368,29 +1390,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}" name="Table1" displayName="Table1" ref="A1:T117" totalsRowShown="0" dataDxfId="30">
-  <autoFilter ref="A1:T117" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}"/>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{85A1F019-9DB7-48AC-AF2B-F0C9FBE637DA}" name="Location" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{545588E2-5E30-4A62-AB93-1DBC57F6BCF8}" name="Business" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{44C3C497-13A6-40FF-AABF-EC930E13E039}" name="Section" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{ED8F8366-2CFD-45B1-B1C2-AA92F55B23F6}" name="Sr_No" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{3C440E90-56BF-4BC4-ACD0-A73E98969A14}" name="Dept_Machine_Name" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{EADE3DD8-7C1C-4874-8032-AD8F2F81A125}" name="Designation" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{292F7B89-A9FA-4B1D-8581-9D4596E679FF}" name="Machine_Count" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{090D3B71-C4CF-432F-B817-104F30316591}" name="Workload" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{9EDB9484-B177-478C-9BA3-4C1AE3030F95}" name="Formulas" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{3A1186F6-9294-4AEC-A543-A07372ADEF4D}" name="BE_Scientific_Manpower" dataDxfId="20"/>
-    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="18"/>
-    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}" name="Table1" displayName="Table1" ref="A1:U117" totalsRowShown="0" dataDxfId="21">
+  <autoFilter ref="A1:U117" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{85A1F019-9DB7-48AC-AF2B-F0C9FBE637DA}" name="Location" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{545588E2-5E30-4A62-AB93-1DBC57F6BCF8}" name="Business" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{44C3C497-13A6-40FF-AABF-EC930E13E039}" name="Section" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{ED8F8366-2CFD-45B1-B1C2-AA92F55B23F6}" name="Sr_No" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{3C440E90-56BF-4BC4-ACD0-A73E98969A14}" name="Dept_Machine_Name" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{EADE3DD8-7C1C-4874-8032-AD8F2F81A125}" name="Designation" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{292F7B89-A9FA-4B1D-8581-9D4596E679FF}" name="Machine_Count" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{C464261F-9918-428A-92D8-8AA20D507764}" name="Manpower_Base_Qty" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{090D3B71-C4CF-432F-B817-104F30316591}" name="Workload" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{9EDB9484-B177-478C-9BA3-4C1AE3030F95}" name="Formulas" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{3A1186F6-9294-4AEC-A543-A07372ADEF4D}" name="BE_Scientific_Manpower" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1421,18 +1444,18 @@
       <calculatedColumnFormula>L2/I2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{7C882653-B2FB-4460-945F-BEC827034FAE}" name="formula_No. of TFO Required/ shift "/>
-    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="31" totalsRowDxfId="30"/>
     <tableColumn id="15" xr3:uid="{65F3003E-C476-4D6D-BE1A-6488E17CDB9D}" name="mpm"/>
-    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="27" totalsRowDxfId="26"/>
     <tableColumn id="18" xr3:uid="{00170897-62B8-4C84-AE04-5EAE44ABC362}" name="kgs/drum/day ">
       <calculatedColumnFormula>Q2*R2*8*60*1.09/(C2*840*2.202)*3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{2DD7DB04-94B4-4773-9E4C-D99D0E582A8C}" name="formula_No. of Drums"/>
-    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="25" totalsRowDxfId="24">
       <calculatedColumnFormula>L2/T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="23" totalsRowDxfId="22"/>
     <tableColumn id="22" xr3:uid="{0459E32F-2AB6-434A-9439-F5F08B7C6254}" name="no. of machines">
       <calculatedColumnFormula>V2/72</calculatedColumnFormula>
     </tableColumn>
@@ -1726,27 +1749,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T117"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U117"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" customWidth="1"/>
-    <col min="5" max="5" width="46.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.44140625" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" customWidth="1"/>
-    <col min="8" max="8" width="48.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="31.5546875" customWidth="1"/>
-    <col min="14" max="14" width="26.21875" customWidth="1"/>
-    <col min="15" max="15" width="18.77734375" customWidth="1"/>
-    <col min="16" max="18" width="11.5546875" customWidth="1"/>
-    <col min="19" max="19" width="12.33203125" customWidth="1"/>
-    <col min="20" max="20" width="38.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.1015625" customWidth="1"/>
+    <col min="2" max="2" width="13.3125" customWidth="1"/>
+    <col min="3" max="3" width="20.1015625" customWidth="1"/>
+    <col min="4" max="4" width="10.1015625" customWidth="1"/>
+    <col min="5" max="5" width="46.7890625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.41796875" customWidth="1"/>
+    <col min="7" max="7" width="20.7890625" customWidth="1"/>
+    <col min="8" max="8" width="23.1015625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.41796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="31.5234375" customWidth="1"/>
+    <col min="15" max="15" width="26.20703125" customWidth="1"/>
+    <col min="16" max="16" width="18.7890625" customWidth="1"/>
+    <col min="17" max="19" width="11.5234375" customWidth="1"/>
+    <col min="20" max="20" width="12.3125" customWidth="1"/>
+    <col min="21" max="21" width="38.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1769,46 +1793,49 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>270</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>284</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>42</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>283</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>5</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1830,23 +1857,20 @@
       <c r="G2">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>46</v>
       </c>
-      <c r="J2">
-        <v>12</v>
-      </c>
-      <c r="N2">
+      <c r="K2">
+        <v>12</v>
+      </c>
+      <c r="O2">
         <v>9</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
       <c r="P2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -1855,13 +1879,16 @@
         <v>3</v>
       </c>
       <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1883,23 +1910,20 @@
       <c r="G3">
         <v>52</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>47</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>7.09</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>9</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>3</v>
@@ -1908,10 +1932,13 @@
         <v>3</v>
       </c>
       <c r="S3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1933,23 +1960,20 @@
       <c r="G4">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>34</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>48</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>3</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>3</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
       <c r="P4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1958,10 +1982,13 @@
         <v>1</v>
       </c>
       <c r="S4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1983,23 +2010,20 @@
       <c r="G5">
         <v>22</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>16.5</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>18</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
       <c r="P5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>6</v>
@@ -2008,10 +2032,13 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2033,23 +2060,20 @@
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>35</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -2058,10 +2082,13 @@
         <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2083,23 +2110,20 @@
       <c r="G7">
         <v>3</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>36</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>51</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>4.5</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -2108,10 +2132,13 @@
         <v>2</v>
       </c>
       <c r="S7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2133,23 +2160,20 @@
       <c r="G8">
         <v>18</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>37</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>52</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>5.4</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>6</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
       <c r="P8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2158,10 +2182,13 @@
         <v>2</v>
       </c>
       <c r="S8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2183,23 +2210,20 @@
       <c r="G9">
         <v>21</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>53</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>15.75</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>15</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
       <c r="P9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -2208,10 +2232,13 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2233,21 +2260,18 @@
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>54</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>3.75</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>4</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
       <c r="P10">
         <v>1</v>
       </c>
@@ -2258,10 +2282,13 @@
         <v>1</v>
       </c>
       <c r="S10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2283,23 +2310,20 @@
       <c r="G11">
         <v>16</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>38</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>55</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>24</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>27</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
       <c r="P11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -2308,13 +2332,16 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2336,23 +2363,20 @@
       <c r="G12">
         <v>16</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>39</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>55</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>24</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>27</v>
       </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
       <c r="P12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -2361,10 +2385,13 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2383,23 +2410,20 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>40</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>155</v>
       </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="N13">
+      <c r="K13">
         <v>3</v>
       </c>
       <c r="O13">
         <v>3</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2410,8 +2434,11 @@
       <c r="S13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2430,23 +2457,20 @@
       <c r="F14" t="s">
         <v>29</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>41</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>147</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>6</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>6</v>
       </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
       <c r="P14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -2455,10 +2479,13 @@
         <v>2</v>
       </c>
       <c r="S14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2477,23 +2504,20 @@
       <c r="F15" t="s">
         <v>31</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>42</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>147</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>6</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>6</v>
       </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
       <c r="P15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <v>2</v>
@@ -2502,10 +2526,13 @@
         <v>2</v>
       </c>
       <c r="S15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2524,16 +2551,13 @@
       <c r="F16" t="s">
         <v>15</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>43</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>271</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="N16">
+      <c r="K16">
         <v>0</v>
       </c>
       <c r="O16">
@@ -2551,11 +2575,14 @@
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16" t="s">
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2577,23 +2604,20 @@
       <c r="G17">
         <v>7</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>97</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>59</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>30</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>30</v>
       </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
       <c r="P17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2602,10 +2626,13 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2627,23 +2654,20 @@
       <c r="G18">
         <v>12</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>98</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>61</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>25</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>25</v>
       </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
       <c r="P18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>8</v>
@@ -2652,10 +2676,13 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2677,23 +2704,20 @@
       <c r="G19">
         <v>18</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>98</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>63</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>54</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>54</v>
       </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
       <c r="P19">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>18</v>
@@ -2702,10 +2726,13 @@
         <v>18</v>
       </c>
       <c r="S19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2727,23 +2754,20 @@
       <c r="G20">
         <v>4</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>99</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>65</v>
       </c>
-      <c r="J20">
-        <v>12</v>
-      </c>
-      <c r="N20">
+      <c r="K20">
         <v>12</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>4</v>
@@ -2752,10 +2776,13 @@
         <v>4</v>
       </c>
       <c r="S20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2774,23 +2801,20 @@
       <c r="F21" t="s">
         <v>15</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>67</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>68</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>18</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>18</v>
       </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
       <c r="P21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -2799,10 +2823,13 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2821,38 +2848,39 @@
       <c r="F22" t="s">
         <v>15</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="4"/>
+      <c r="H22">
         <v>52608</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>70</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>71</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>41</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>41</v>
       </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
       <c r="P22">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>14</v>
       </c>
       <c r="R22">
+        <v>14</v>
+      </c>
+      <c r="S22">
         <v>13</v>
       </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -2874,23 +2902,20 @@
       <c r="G23">
         <v>7</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>73</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>74</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>6</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>6</v>
       </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
       <c r="P23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>2</v>
@@ -2899,10 +2924,13 @@
         <v>2</v>
       </c>
       <c r="S23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2924,23 +2952,20 @@
       <c r="G24">
         <v>12</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>76</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>77</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>6</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>6</v>
       </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
       <c r="P24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>2</v>
@@ -2949,10 +2974,13 @@
         <v>2</v>
       </c>
       <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -2974,23 +3002,20 @@
       <c r="G25">
         <v>18</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>79</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>80</v>
       </c>
-      <c r="J25">
-        <v>12</v>
-      </c>
-      <c r="N25">
+      <c r="K25">
         <v>12</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -2999,10 +3024,13 @@
         <v>4</v>
       </c>
       <c r="S25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3024,23 +3052,20 @@
       <c r="G26">
         <v>4</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>82</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>83</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>3</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>3</v>
       </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
       <c r="P26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -3049,10 +3074,13 @@
         <v>1</v>
       </c>
       <c r="S26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3071,20 +3099,17 @@
       <c r="F27" t="s">
         <v>84</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>169</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>9</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>9</v>
       </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
       <c r="P27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -3093,13 +3118,16 @@
         <v>3</v>
       </c>
       <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3118,23 +3146,21 @@
       <c r="F28" t="s">
         <v>15</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="4"/>
+      <c r="H28">
         <v>52608</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>147</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>6</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>6</v>
       </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
       <c r="P28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>2</v>
@@ -3143,13 +3169,16 @@
         <v>2</v>
       </c>
       <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28" t="s">
+        <v>2</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3168,20 +3197,17 @@
       <c r="F29" t="s">
         <v>88</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>147</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>6</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>6</v>
       </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
       <c r="P29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -3190,13 +3216,16 @@
         <v>2</v>
       </c>
       <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29" t="s">
+        <v>2</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3215,20 +3244,17 @@
       <c r="F30" t="s">
         <v>42</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>147</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>6</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>6</v>
       </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
       <c r="P30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -3237,13 +3263,16 @@
         <v>2</v>
       </c>
       <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30" t="s">
+        <v>2</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3262,20 +3291,17 @@
       <c r="F31" t="s">
         <v>42</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>147</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>6</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>6</v>
       </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
       <c r="P31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>2</v>
@@ -3284,13 +3310,16 @@
         <v>2</v>
       </c>
       <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31" t="s">
+        <v>2</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3306,23 +3335,20 @@
       <c r="E32" t="s">
         <v>91</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>92</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>147</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>6</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>6</v>
       </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
       <c r="P32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>2</v>
@@ -3331,13 +3357,16 @@
         <v>2</v>
       </c>
       <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32" t="s">
+        <v>2</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -3353,23 +3382,20 @@
       <c r="E33" t="s">
         <v>93</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>94</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>147</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>6</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>6</v>
       </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
       <c r="P33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>2</v>
@@ -3378,13 +3404,16 @@
         <v>2</v>
       </c>
       <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33" t="s">
+        <v>2</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3400,23 +3429,20 @@
       <c r="E34" t="s">
         <v>95</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>96</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>147</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>6</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>6</v>
       </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
       <c r="P34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -3425,13 +3451,16 @@
         <v>2</v>
       </c>
       <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34" t="s">
+        <v>2</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -3450,20 +3479,17 @@
       <c r="F35" t="s">
         <v>42</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>140</v>
       </c>
-      <c r="J35">
-        <v>12</v>
-      </c>
-      <c r="N35">
+      <c r="K35">
         <v>12</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -3472,10 +3498,13 @@
         <v>4</v>
       </c>
       <c r="S35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -3494,23 +3523,20 @@
       <c r="G36">
         <v>29</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>102</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>103</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>22</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>21</v>
       </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
       <c r="P36">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>7</v>
@@ -3519,10 +3545,13 @@
         <v>7</v>
       </c>
       <c r="S36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -3541,23 +3570,20 @@
       <c r="G37">
         <v>6</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>268</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>105</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>30</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>30</v>
       </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
       <c r="P37">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -3566,10 +3592,13 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -3585,20 +3614,17 @@
       <c r="E38" t="s">
         <v>106</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>147</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>6</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>6</v>
       </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
       <c r="P38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -3607,13 +3633,16 @@
         <v>2</v>
       </c>
       <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38" t="s">
+        <v>2</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -3629,20 +3658,17 @@
       <c r="E39" t="s">
         <v>9</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>147</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>6</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>6</v>
       </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
       <c r="P39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -3651,13 +3677,16 @@
         <v>2</v>
       </c>
       <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39" t="s">
+        <v>2</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -3676,20 +3705,17 @@
       <c r="F40" t="s">
         <v>84</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>155</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>3</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>3</v>
       </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
       <c r="P40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>1</v>
@@ -3698,13 +3724,16 @@
         <v>1</v>
       </c>
       <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40" t="s">
+        <v>1</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -3723,20 +3752,17 @@
       <c r="F41" t="s">
         <v>107</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>271</v>
       </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="N41">
+      <c r="K41">
         <v>1</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -3747,11 +3773,14 @@
       <c r="S41">
         <v>0</v>
       </c>
-      <c r="T41" t="s">
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -3770,20 +3799,17 @@
       <c r="F42" t="s">
         <v>42</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>155</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>3</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>3</v>
       </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
       <c r="P42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <v>1</v>
@@ -3792,13 +3818,16 @@
         <v>1</v>
       </c>
       <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42" t="s">
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3817,20 +3846,17 @@
       <c r="F43" t="s">
         <v>15</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>155</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>3</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>3</v>
       </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
       <c r="P43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -3839,13 +3865,16 @@
         <v>1</v>
       </c>
       <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43" t="s">
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -3864,20 +3893,17 @@
       <c r="F44" t="s">
         <v>29</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>155</v>
       </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="N44">
+      <c r="K44">
         <v>0</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3886,13 +3912,16 @@
         <v>1</v>
       </c>
       <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44" t="s">
+        <v>1</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -3911,20 +3940,17 @@
       <c r="F45" t="s">
         <v>15</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>155</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>3</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>3</v>
       </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
       <c r="P45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45">
         <v>1</v>
@@ -3933,13 +3959,16 @@
         <v>1</v>
       </c>
       <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3958,23 +3987,20 @@
       <c r="F46" t="s">
         <v>112</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>113</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>147</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>6</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>6</v>
       </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
       <c r="P46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -3983,13 +4009,16 @@
         <v>2</v>
       </c>
       <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46" t="s">
+        <v>2</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -4008,23 +4037,20 @@
       <c r="F47" t="s">
         <v>115</v>
       </c>
-      <c r="H47" t="s">
+      <c r="I47" t="s">
         <v>116</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>147</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>3</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>3</v>
       </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
       <c r="P47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q47">
         <v>2</v>
@@ -4033,13 +4059,16 @@
         <v>2</v>
       </c>
       <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47" t="s">
+        <v>2</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -4061,23 +4090,20 @@
       <c r="G48">
         <v>8</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
         <v>120</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>122</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>24</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>24</v>
       </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
       <c r="P48">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>8</v>
@@ -4086,10 +4112,13 @@
         <v>8</v>
       </c>
       <c r="S48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -4108,20 +4137,17 @@
       <c r="F49" t="s">
         <v>29</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>155</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>3</v>
       </c>
-      <c r="N49">
+      <c r="O49">
         <v>3</v>
       </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
       <c r="P49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>1</v>
@@ -4130,10 +4156,13 @@
         <v>1</v>
       </c>
       <c r="S49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -4152,20 +4181,17 @@
       <c r="F50" t="s">
         <v>121</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>271</v>
       </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="N50">
+      <c r="K50">
         <v>1</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -4176,8 +4202,11 @@
       <c r="S50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -4196,36 +4225,37 @@
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
-      <c r="I51" s="4" t="s">
+      <c r="I51" s="4"/>
+      <c r="J51" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="J51" s="4">
+      <c r="K51" s="4">
         <v>14</v>
       </c>
-      <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
-      <c r="N51" s="4">
+      <c r="N51" s="4"/>
+      <c r="O51" s="4">
         <v>14</v>
       </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="4">
-        <v>7</v>
+      <c r="P51" s="1">
+        <v>0</v>
       </c>
       <c r="Q51" s="4">
         <v>7</v>
       </c>
       <c r="R51" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S51" s="4">
         <v>0</v>
       </c>
-      <c r="T51" s="4"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T51" s="4">
+        <v>0</v>
+      </c>
+      <c r="U51" s="4"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
@@ -4244,36 +4274,37 @@
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
-      <c r="I52" s="4" t="s">
+      <c r="I52" s="4"/>
+      <c r="J52" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="J52" s="4">
+      <c r="K52" s="4">
         <v>6</v>
       </c>
-      <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
-      <c r="N52" s="4">
+      <c r="N52" s="4"/>
+      <c r="O52" s="4">
         <v>6</v>
       </c>
-      <c r="O52" s="1">
-        <v>0</v>
-      </c>
-      <c r="P52" s="4">
-        <v>3</v>
+      <c r="P52" s="1">
+        <v>0</v>
       </c>
       <c r="Q52" s="4">
         <v>3</v>
       </c>
       <c r="R52" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S52" s="4">
         <v>0</v>
       </c>
-      <c r="T52" s="4"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T52" s="4">
+        <v>0</v>
+      </c>
+      <c r="U52" s="4"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>11</v>
       </c>
@@ -4292,36 +4323,37 @@
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
-      <c r="I53" s="4" t="s">
+      <c r="I53" s="4"/>
+      <c r="J53" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="J53" s="4">
+      <c r="K53" s="4">
         <v>6</v>
       </c>
-      <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="4">
+      <c r="N53" s="4"/>
+      <c r="O53" s="4">
         <v>6</v>
       </c>
-      <c r="O53" s="1">
-        <v>0</v>
-      </c>
-      <c r="P53" s="4">
-        <v>3</v>
+      <c r="P53" s="1">
+        <v>0</v>
       </c>
       <c r="Q53" s="4">
         <v>3</v>
       </c>
       <c r="R53" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S53" s="4">
         <v>0</v>
       </c>
-      <c r="T53" s="4"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T53" s="4">
+        <v>0</v>
+      </c>
+      <c r="U53" s="4"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>11</v>
       </c>
@@ -4340,23 +4372,21 @@
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="1"/>
+      <c r="J54" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J54" s="1">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1"/>
+      <c r="K54" s="1">
+        <v>1</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
-      <c r="N54" s="1">
-        <v>1</v>
-      </c>
+      <c r="N54" s="1"/>
       <c r="O54" s="1">
         <v>1</v>
       </c>
       <c r="P54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="1">
         <v>0</v>
@@ -4367,9 +4397,12 @@
       <c r="S54" s="1">
         <v>0</v>
       </c>
-      <c r="T54" s="1"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="1"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>11</v>
       </c>
@@ -4387,26 +4420,24 @@
         <v>143</v>
       </c>
       <c r="G55" s="1"/>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="1"/>
+      <c r="I55" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J55" s="1">
-        <v>12</v>
-      </c>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1">
+        <v>12</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
-      <c r="N55" s="1">
-        <v>12</v>
-      </c>
+      <c r="N55" s="1"/>
       <c r="O55" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P55" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="1">
         <v>4</v>
@@ -4415,11 +4446,14 @@
         <v>4</v>
       </c>
       <c r="S55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="1"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>11</v>
       </c>
@@ -4437,26 +4471,24 @@
         <v>145</v>
       </c>
       <c r="G56" s="1"/>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="1"/>
+      <c r="I56" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="J56" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J56" s="1">
+      <c r="K56" s="1">
         <v>6</v>
       </c>
-      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
-      <c r="N56" s="1">
+      <c r="N56" s="1"/>
+      <c r="O56" s="1">
         <v>6</v>
       </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
       <c r="P56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="1">
         <v>2</v>
@@ -4465,11 +4497,14 @@
         <v>2</v>
       </c>
       <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="1"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>11</v>
       </c>
@@ -4487,26 +4522,24 @@
         <v>148</v>
       </c>
       <c r="G57" s="1"/>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="1"/>
+      <c r="I57" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="J57" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="J57" s="1">
-        <v>2</v>
-      </c>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1">
+        <v>2</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
-      <c r="N57" s="1">
-        <v>2</v>
-      </c>
+      <c r="N57" s="1"/>
       <c r="O57" s="1">
         <v>2</v>
       </c>
       <c r="P57" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" s="1">
         <v>0</v>
@@ -4517,9 +4550,12 @@
       <c r="S57" s="1">
         <v>0</v>
       </c>
-      <c r="T57" s="1"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>11</v>
       </c>
@@ -4537,41 +4573,42 @@
         <v>150</v>
       </c>
       <c r="G58" s="1"/>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="1"/>
+      <c r="I58" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J58" s="1">
-        <v>12</v>
-      </c>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1">
+        <v>12</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
-      <c r="N58" s="1">
+      <c r="N58" s="1"/>
+      <c r="O58" s="1">
         <v>14</v>
       </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
       <c r="P58" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="1">
         <v>5</v>
       </c>
       <c r="R58" s="1">
+        <v>5</v>
+      </c>
+      <c r="S58" s="1">
         <v>4</v>
       </c>
-      <c r="S58" s="1">
-        <v>0</v>
-      </c>
-      <c r="T58" s="1" t="s">
+      <c r="T58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>11</v>
       </c>
@@ -4589,26 +4626,24 @@
         <v>153</v>
       </c>
       <c r="G59" s="1"/>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="1"/>
+      <c r="I59" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="J59" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J59" s="1">
+      <c r="K59" s="1">
         <v>3</v>
       </c>
-      <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
-      <c r="N59" s="1">
+      <c r="N59" s="1"/>
+      <c r="O59" s="1">
         <v>3</v>
       </c>
-      <c r="O59" s="1">
-        <v>0</v>
-      </c>
       <c r="P59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="1">
         <v>1</v>
@@ -4617,11 +4652,14 @@
         <v>1</v>
       </c>
       <c r="S59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T59" s="1">
+        <v>0</v>
+      </c>
+      <c r="U59" s="1"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>11</v>
       </c>
@@ -4639,26 +4677,24 @@
         <v>156</v>
       </c>
       <c r="G60" s="1"/>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="1"/>
+      <c r="I60" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="J60" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J60" s="1">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1"/>
+      <c r="K60" s="1">
+        <v>1</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
-      <c r="N60" s="1">
-        <v>1</v>
-      </c>
+      <c r="N60" s="1"/>
       <c r="O60" s="1">
         <v>1</v>
       </c>
       <c r="P60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="1">
         <v>0</v>
@@ -4669,9 +4705,12 @@
       <c r="S60" s="1">
         <v>0</v>
       </c>
-      <c r="T60" s="1"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>11</v>
       </c>
@@ -4689,26 +4728,24 @@
         <v>159</v>
       </c>
       <c r="G61" s="1"/>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="1"/>
+      <c r="I61" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="J61" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J61" s="1">
+      <c r="K61" s="1">
         <v>3</v>
       </c>
-      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
-      <c r="N61" s="1">
+      <c r="N61" s="1"/>
+      <c r="O61" s="1">
         <v>3</v>
       </c>
-      <c r="O61" s="1">
-        <v>0</v>
-      </c>
       <c r="P61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="1">
         <v>1</v>
@@ -4717,11 +4754,14 @@
         <v>1</v>
       </c>
       <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="1"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+      <c r="U61" s="1"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>11</v>
       </c>
@@ -4739,21 +4779,19 @@
         <v>161</v>
       </c>
       <c r="G62" s="1"/>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="1"/>
+      <c r="I62" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="J62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J62" s="1">
+      <c r="K62" s="1">
         <v>3</v>
       </c>
-      <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
-      <c r="N62" s="1">
-        <v>0</v>
-      </c>
+      <c r="N62" s="1"/>
       <c r="O62" s="1">
         <v>0</v>
       </c>
@@ -4769,11 +4807,14 @@
       <c r="S62" s="1">
         <v>0</v>
       </c>
-      <c r="T62" s="1" t="s">
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>11</v>
       </c>
@@ -4791,26 +4832,24 @@
         <v>163</v>
       </c>
       <c r="G63" s="1"/>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="1"/>
+      <c r="I63" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J63" s="1">
-        <v>12</v>
-      </c>
-      <c r="K63" s="1"/>
+      <c r="K63" s="1">
+        <v>12</v>
+      </c>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
-      <c r="N63" s="1">
-        <v>12</v>
-      </c>
+      <c r="N63" s="1"/>
       <c r="O63" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P63" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="1">
         <v>4</v>
@@ -4819,11 +4858,14 @@
         <v>4</v>
       </c>
       <c r="S63" s="1">
-        <v>0</v>
-      </c>
-      <c r="T63" s="1"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>11</v>
       </c>
@@ -4841,26 +4883,24 @@
         <v>166</v>
       </c>
       <c r="G64" s="1"/>
-      <c r="H64" s="1" t="s">
+      <c r="H64" s="1"/>
+      <c r="I64" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="J64" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J64" s="1">
+      <c r="K64" s="1">
         <v>3</v>
       </c>
-      <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
-      <c r="N64" s="1">
+      <c r="N64" s="1"/>
+      <c r="O64" s="1">
         <v>3</v>
       </c>
-      <c r="O64" s="1">
-        <v>0</v>
-      </c>
       <c r="P64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="1">
         <v>1</v>
@@ -4869,11 +4909,14 @@
         <v>1</v>
       </c>
       <c r="S64" s="1">
-        <v>0</v>
-      </c>
-      <c r="T64" s="1"/>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>11</v>
       </c>
@@ -4891,26 +4934,24 @@
         <v>167</v>
       </c>
       <c r="G65" s="1"/>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="1"/>
+      <c r="I65" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="J65" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J65" s="1">
+      <c r="K65" s="1">
         <v>9</v>
       </c>
-      <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
-      <c r="N65" s="1">
+      <c r="N65" s="1"/>
+      <c r="O65" s="1">
         <v>9</v>
       </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
       <c r="P65" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="1">
         <v>3</v>
@@ -4919,11 +4960,14 @@
         <v>3</v>
       </c>
       <c r="S65" s="1">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>11</v>
       </c>
@@ -4941,41 +4985,42 @@
         <v>138</v>
       </c>
       <c r="G66" s="1"/>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="1"/>
+      <c r="I66" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="J66" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J66" s="1">
+      <c r="K66" s="1">
         <v>4</v>
       </c>
-      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
-      <c r="N66" s="1">
+      <c r="N66" s="1"/>
+      <c r="O66" s="1">
         <v>4</v>
       </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
       <c r="P66" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="1">
         <v>2</v>
       </c>
       <c r="R66" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S66" s="1">
         <v>0</v>
       </c>
-      <c r="T66" s="1" t="s">
+      <c r="T66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
         <v>11</v>
       </c>
@@ -4993,21 +5038,19 @@
         <v>29</v>
       </c>
       <c r="G67" s="1"/>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="1"/>
+      <c r="I67" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="J67" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J67" s="1">
-        <v>1</v>
-      </c>
-      <c r="K67" s="1"/>
+      <c r="K67" s="1">
+        <v>1</v>
+      </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="N67" s="1">
-        <v>0</v>
-      </c>
+      <c r="N67" s="1"/>
       <c r="O67" s="1">
         <v>0</v>
       </c>
@@ -5023,11 +5066,14 @@
       <c r="S67" s="1">
         <v>0</v>
       </c>
-      <c r="T67" s="1" t="s">
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>11</v>
       </c>
@@ -5045,41 +5091,42 @@
         <v>175</v>
       </c>
       <c r="G68" s="1"/>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="1"/>
+      <c r="I68" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="J68" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J68" s="1">
+      <c r="K68" s="1">
         <v>8</v>
       </c>
-      <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
-      <c r="N68" s="1">
+      <c r="N68" s="1"/>
+      <c r="O68" s="1">
         <v>8</v>
       </c>
-      <c r="O68" s="1">
-        <v>0</v>
-      </c>
       <c r="P68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="1">
         <v>4</v>
       </c>
       <c r="R68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S68" s="1">
         <v>0</v>
       </c>
-      <c r="T68" s="1" t="s">
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>11</v>
       </c>
@@ -5097,26 +5144,24 @@
         <v>179</v>
       </c>
       <c r="G69" s="1"/>
-      <c r="H69" s="1" t="s">
+      <c r="H69" s="1"/>
+      <c r="I69" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="J69" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J69" s="1">
-        <v>12</v>
-      </c>
-      <c r="K69" s="1"/>
+      <c r="K69" s="1">
+        <v>12</v>
+      </c>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
-      <c r="N69" s="1">
-        <v>12</v>
-      </c>
+      <c r="N69" s="1"/>
       <c r="O69" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P69" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="1">
         <v>4</v>
@@ -5125,11 +5170,14 @@
         <v>4</v>
       </c>
       <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="1"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T69" s="1">
+        <v>0</v>
+      </c>
+      <c r="U69" s="1"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
         <v>11</v>
       </c>
@@ -5147,26 +5195,24 @@
         <v>180</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="1" t="s">
+      <c r="H70" s="1"/>
+      <c r="I70" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J70" s="1">
-        <v>12</v>
-      </c>
-      <c r="K70" s="1"/>
+      <c r="K70" s="1">
+        <v>12</v>
+      </c>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
-      <c r="N70" s="1">
-        <v>12</v>
-      </c>
+      <c r="N70" s="1"/>
       <c r="O70" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="1">
         <v>4</v>
@@ -5175,11 +5221,14 @@
         <v>4</v>
       </c>
       <c r="S70" s="1">
-        <v>0</v>
-      </c>
-      <c r="T70" s="1"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T70" s="1">
+        <v>0</v>
+      </c>
+      <c r="U70" s="1"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -5197,26 +5246,24 @@
         <v>182</v>
       </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="1" t="s">
+      <c r="H71" s="1"/>
+      <c r="I71" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="J71" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J71" s="1">
+      <c r="K71" s="1">
         <v>6</v>
       </c>
-      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
-      <c r="N71" s="1">
+      <c r="N71" s="1"/>
+      <c r="O71" s="1">
         <v>6</v>
       </c>
-      <c r="O71" s="1">
-        <v>0</v>
-      </c>
       <c r="P71" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="1">
         <v>2</v>
@@ -5225,11 +5272,14 @@
         <v>2</v>
       </c>
       <c r="S71" s="1">
-        <v>0</v>
-      </c>
-      <c r="T71" s="1"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T71" s="1">
+        <v>0</v>
+      </c>
+      <c r="U71" s="1"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
@@ -5247,41 +5297,42 @@
         <v>184</v>
       </c>
       <c r="G72" s="1"/>
-      <c r="H72" s="1" t="s">
+      <c r="H72" s="1"/>
+      <c r="I72" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J72" s="1">
+      <c r="K72" s="1">
         <v>3</v>
       </c>
-      <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
-      <c r="N72" s="1">
+      <c r="N72" s="1"/>
+      <c r="O72" s="1">
         <v>4</v>
       </c>
-      <c r="O72" s="1">
-        <v>0</v>
-      </c>
       <c r="P72" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72" s="1">
         <v>1</v>
       </c>
       <c r="S72" s="1">
-        <v>0</v>
-      </c>
-      <c r="T72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T72" s="1">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>11</v>
       </c>
@@ -5299,26 +5350,24 @@
         <v>186</v>
       </c>
       <c r="G73" s="1"/>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="1"/>
+      <c r="I73" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J73" s="1">
+      <c r="K73" s="1">
         <v>3</v>
       </c>
-      <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
-      <c r="N73" s="1">
+      <c r="N73" s="1"/>
+      <c r="O73" s="1">
         <v>3</v>
       </c>
-      <c r="O73" s="1">
-        <v>0</v>
-      </c>
       <c r="P73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="1">
         <v>1</v>
@@ -5327,11 +5376,14 @@
         <v>1</v>
       </c>
       <c r="S73" s="1">
-        <v>0</v>
-      </c>
-      <c r="T73" s="1"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T73" s="1">
+        <v>0</v>
+      </c>
+      <c r="U73" s="1"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
@@ -5349,39 +5401,40 @@
         <v>187</v>
       </c>
       <c r="G74" s="1"/>
-      <c r="H74" s="1" t="s">
+      <c r="H74" s="1"/>
+      <c r="I74" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="J74" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J74" s="1">
-        <v>2</v>
-      </c>
-      <c r="K74" s="1"/>
+      <c r="K74" s="1">
+        <v>2</v>
+      </c>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-      <c r="N74" s="1">
-        <v>2</v>
-      </c>
+      <c r="N74" s="1"/>
       <c r="O74" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="1">
         <v>1</v>
       </c>
       <c r="R74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" s="1">
         <v>0</v>
       </c>
-      <c r="T74" s="1"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T74" s="1">
+        <v>0</v>
+      </c>
+      <c r="U74" s="1"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
@@ -5399,41 +5452,42 @@
         <v>190</v>
       </c>
       <c r="G75" s="1"/>
-      <c r="H75" s="1" t="s">
+      <c r="H75" s="1"/>
+      <c r="I75" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="J75" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="J75" s="1">
+      <c r="K75" s="1">
         <v>9</v>
       </c>
-      <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
-      <c r="N75" s="1">
+      <c r="N75" s="1"/>
+      <c r="O75" s="1">
         <v>7</v>
       </c>
-      <c r="O75" s="1">
-        <v>0</v>
-      </c>
       <c r="P75" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="1">
         <v>3</v>
       </c>
       <c r="R75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S75" s="1">
-        <v>0</v>
-      </c>
-      <c r="T75" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T75" s="1">
+        <v>0</v>
+      </c>
+      <c r="U75" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
         <v>11</v>
       </c>
@@ -5451,26 +5505,24 @@
         <v>192</v>
       </c>
       <c r="G76" s="1"/>
-      <c r="H76" s="1" t="s">
+      <c r="H76" s="1"/>
+      <c r="I76" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="J76" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J76" s="1">
+      <c r="K76" s="1">
         <v>3</v>
       </c>
-      <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
-      <c r="N76" s="1">
+      <c r="N76" s="1"/>
+      <c r="O76" s="1">
         <v>3</v>
       </c>
-      <c r="O76" s="1">
-        <v>0</v>
-      </c>
       <c r="P76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="1">
         <v>1</v>
@@ -5479,11 +5531,14 @@
         <v>1</v>
       </c>
       <c r="S76" s="1">
-        <v>0</v>
-      </c>
-      <c r="T76" s="1"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T76" s="1">
+        <v>0</v>
+      </c>
+      <c r="U76" s="1"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
         <v>11</v>
       </c>
@@ -5501,26 +5556,24 @@
         <v>193</v>
       </c>
       <c r="G77" s="1"/>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="1"/>
+      <c r="I77" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J77" s="1">
+      <c r="K77" s="1">
         <v>3</v>
       </c>
-      <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
-      <c r="N77" s="1">
+      <c r="N77" s="1"/>
+      <c r="O77" s="1">
         <v>3</v>
       </c>
-      <c r="O77" s="1">
-        <v>0</v>
-      </c>
       <c r="P77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="1">
         <v>1</v>
@@ -5529,11 +5582,14 @@
         <v>1</v>
       </c>
       <c r="S77" s="1">
-        <v>0</v>
-      </c>
-      <c r="T77" s="1"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T77" s="1">
+        <v>0</v>
+      </c>
+      <c r="U77" s="1"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>11</v>
       </c>
@@ -5551,41 +5607,42 @@
         <v>148</v>
       </c>
       <c r="G78" s="1"/>
-      <c r="H78" s="1" t="s">
+      <c r="H78" s="1"/>
+      <c r="I78" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="J78" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J78" s="1">
+      <c r="K78" s="1">
         <v>10</v>
       </c>
-      <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-      <c r="N78" s="1">
+      <c r="N78" s="1"/>
+      <c r="O78" s="1">
         <v>10</v>
       </c>
-      <c r="O78" s="1">
-        <v>0</v>
-      </c>
       <c r="P78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1">
         <v>4</v>
-      </c>
-      <c r="Q78" s="1">
-        <v>3</v>
       </c>
       <c r="R78" s="1">
         <v>3</v>
       </c>
       <c r="S78" s="1">
-        <v>0</v>
-      </c>
-      <c r="T78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T78" s="1">
+        <v>0</v>
+      </c>
+      <c r="U78" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>11</v>
       </c>
@@ -5606,21 +5663,19 @@
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
-      <c r="I79" t="s">
+      <c r="I79" s="4"/>
+      <c r="J79" t="s">
         <v>155</v>
       </c>
-      <c r="J79" s="4"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
-      <c r="N79" s="4">
-        <v>1</v>
-      </c>
+      <c r="N79" s="4"/>
       <c r="O79" s="4">
         <v>1</v>
       </c>
       <c r="P79" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" s="4">
         <v>0</v>
@@ -5631,9 +5686,12 @@
       <c r="S79" s="4">
         <v>0</v>
       </c>
-      <c r="T79" s="4"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T79" s="4">
+        <v>0</v>
+      </c>
+      <c r="U79" s="4"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
@@ -5654,21 +5712,19 @@
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
-      <c r="I80" t="s">
+      <c r="I80" s="4"/>
+      <c r="J80" t="s">
         <v>274</v>
       </c>
-      <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
-      <c r="N80" s="4">
-        <v>9</v>
-      </c>
+      <c r="N80" s="4"/>
       <c r="O80" s="4">
         <v>9</v>
       </c>
       <c r="P80" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q80" s="4">
         <v>0</v>
@@ -5679,9 +5735,12 @@
       <c r="S80" s="4">
         <v>0</v>
       </c>
-      <c r="T80" s="4"/>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T80" s="4">
+        <v>0</v>
+      </c>
+      <c r="U80" s="4"/>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>11</v>
       </c>
@@ -5702,18 +5761,16 @@
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
-      <c r="I81" t="s">
+      <c r="I81" s="4"/>
+      <c r="J81" t="s">
         <v>252</v>
       </c>
-      <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
-      <c r="N81" s="4">
-        <v>2</v>
-      </c>
+      <c r="N81" s="4"/>
       <c r="O81" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P81" s="4">
         <v>0</v>
@@ -5727,9 +5784,12 @@
       <c r="S81" s="4">
         <v>0</v>
       </c>
-      <c r="T81" s="4"/>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T81" s="4">
+        <v>0</v>
+      </c>
+      <c r="U81" s="4"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>11</v>
       </c>
@@ -5750,21 +5810,19 @@
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
-      <c r="I82" t="s">
+      <c r="I82" s="4"/>
+      <c r="J82" t="s">
         <v>253</v>
       </c>
-      <c r="J82" s="4"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
-      <c r="N82" s="4">
-        <v>1</v>
-      </c>
+      <c r="N82" s="4"/>
       <c r="O82" s="4">
         <v>1</v>
       </c>
       <c r="P82" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="4">
         <v>0</v>
@@ -5775,9 +5833,12 @@
       <c r="S82" s="4">
         <v>0</v>
       </c>
-      <c r="T82" s="4"/>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T82" s="4">
+        <v>0</v>
+      </c>
+      <c r="U82" s="4"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>11</v>
       </c>
@@ -5798,21 +5859,19 @@
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
-      <c r="I83" t="s">
+      <c r="I83" s="4"/>
+      <c r="J83" t="s">
         <v>275</v>
       </c>
-      <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
-      <c r="N83" s="4">
-        <v>6</v>
-      </c>
+      <c r="N83" s="4"/>
       <c r="O83" s="4">
         <v>6</v>
       </c>
       <c r="P83" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q83" s="4">
         <v>0</v>
@@ -5823,9 +5882,12 @@
       <c r="S83" s="4">
         <v>0</v>
       </c>
-      <c r="T83" s="4"/>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T83" s="4">
+        <v>0</v>
+      </c>
+      <c r="U83" s="4"/>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
         <v>11</v>
       </c>
@@ -5846,21 +5908,19 @@
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
-      <c r="I84" t="s">
+      <c r="I84" s="4"/>
+      <c r="J84" t="s">
         <v>155</v>
       </c>
-      <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
-      <c r="N84" s="4">
+      <c r="N84" s="4"/>
+      <c r="O84" s="4">
         <v>3</v>
       </c>
-      <c r="O84" s="4">
-        <v>0</v>
-      </c>
       <c r="P84" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="4">
         <v>1</v>
@@ -5869,11 +5929,14 @@
         <v>1</v>
       </c>
       <c r="S84" s="4">
-        <v>0</v>
-      </c>
-      <c r="T84" s="4"/>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T84" s="4">
+        <v>0</v>
+      </c>
+      <c r="U84" s="4"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>11</v>
       </c>
@@ -5894,21 +5957,19 @@
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
-      <c r="I85" t="s">
+      <c r="I85" s="4"/>
+      <c r="J85" t="s">
         <v>252</v>
       </c>
-      <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
-      <c r="N85" s="4">
-        <v>2</v>
-      </c>
+      <c r="N85" s="4"/>
       <c r="O85" s="4">
         <v>2</v>
       </c>
       <c r="P85" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q85" s="4">
         <v>0</v>
@@ -5919,9 +5980,12 @@
       <c r="S85" s="4">
         <v>0</v>
       </c>
-      <c r="T85" s="4"/>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T85" s="4">
+        <v>0</v>
+      </c>
+      <c r="U85" s="4"/>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>11</v>
       </c>
@@ -5942,21 +6006,19 @@
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
-      <c r="I86" t="s">
+      <c r="I86" s="4"/>
+      <c r="J86" t="s">
         <v>274</v>
       </c>
-      <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
-      <c r="N86" s="4">
-        <v>9</v>
-      </c>
+      <c r="N86" s="4"/>
       <c r="O86" s="4">
         <v>9</v>
       </c>
       <c r="P86" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q86" s="4">
         <v>0</v>
@@ -5967,9 +6029,12 @@
       <c r="S86" s="4">
         <v>0</v>
       </c>
-      <c r="T86" s="4"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T86" s="4">
+        <v>0</v>
+      </c>
+      <c r="U86" s="4"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
         <v>11</v>
       </c>
@@ -5990,21 +6055,19 @@
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
-      <c r="I87" t="s">
+      <c r="I87" s="4"/>
+      <c r="J87" t="s">
         <v>155</v>
       </c>
-      <c r="J87" s="4"/>
       <c r="K87" s="4"/>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
-      <c r="N87" s="4">
+      <c r="N87" s="4"/>
+      <c r="O87" s="4">
         <v>3</v>
       </c>
-      <c r="O87" s="4">
-        <v>0</v>
-      </c>
       <c r="P87" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="4">
         <v>1</v>
@@ -6013,11 +6076,14 @@
         <v>1</v>
       </c>
       <c r="S87" s="4">
-        <v>0</v>
-      </c>
-      <c r="T87" s="4"/>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T87" s="4">
+        <v>0</v>
+      </c>
+      <c r="U87" s="4"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>11</v>
       </c>
@@ -6038,21 +6104,19 @@
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
-      <c r="I88" t="s">
+      <c r="I88" s="4"/>
+      <c r="J88" t="s">
         <v>155</v>
       </c>
-      <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
-      <c r="N88" s="4">
+      <c r="N88" s="4"/>
+      <c r="O88" s="4">
         <v>3</v>
       </c>
-      <c r="O88" s="4">
-        <v>0</v>
-      </c>
       <c r="P88" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88" s="4">
         <v>1</v>
@@ -6061,11 +6125,14 @@
         <v>1</v>
       </c>
       <c r="S88" s="4">
-        <v>0</v>
-      </c>
-      <c r="T88" s="4"/>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T88" s="4">
+        <v>0</v>
+      </c>
+      <c r="U88" s="4"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>11</v>
       </c>
@@ -6086,21 +6153,19 @@
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
-      <c r="I89" t="s">
+      <c r="I89" s="4"/>
+      <c r="J89" t="s">
         <v>252</v>
       </c>
-      <c r="J89" s="4"/>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
-      <c r="N89" s="4">
-        <v>2</v>
-      </c>
+      <c r="N89" s="4"/>
       <c r="O89" s="4">
         <v>2</v>
       </c>
       <c r="P89" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="4">
         <v>0</v>
@@ -6111,9 +6176,12 @@
       <c r="S89" s="4">
         <v>0</v>
       </c>
-      <c r="T89" s="4"/>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T89" s="4">
+        <v>0</v>
+      </c>
+      <c r="U89" s="4"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
@@ -6134,21 +6202,19 @@
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
-      <c r="I90" t="s">
+      <c r="I90" s="4"/>
+      <c r="J90" t="s">
         <v>252</v>
       </c>
-      <c r="J90" s="4"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
-      <c r="N90" s="4">
-        <v>2</v>
-      </c>
+      <c r="N90" s="4"/>
       <c r="O90" s="4">
         <v>2</v>
       </c>
       <c r="P90" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="4">
         <v>0</v>
@@ -6159,9 +6225,12 @@
       <c r="S90" s="4">
         <v>0</v>
       </c>
-      <c r="T90" s="4"/>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T90" s="4">
+        <v>0</v>
+      </c>
+      <c r="U90" s="4"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>11</v>
       </c>
@@ -6182,21 +6251,19 @@
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
-      <c r="I91" t="s">
+      <c r="I91" s="4"/>
+      <c r="J91" t="s">
         <v>252</v>
       </c>
-      <c r="J91" s="4"/>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
-      <c r="N91" s="4">
-        <v>2</v>
-      </c>
+      <c r="N91" s="4"/>
       <c r="O91" s="4">
         <v>2</v>
       </c>
       <c r="P91" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="4">
         <v>0</v>
@@ -6207,9 +6274,12 @@
       <c r="S91" s="4">
         <v>0</v>
       </c>
-      <c r="T91" s="4"/>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T91" s="4">
+        <v>0</v>
+      </c>
+      <c r="U91" s="4"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>11</v>
       </c>
@@ -6230,21 +6300,19 @@
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
-      <c r="I92" t="s">
+      <c r="I92" s="4"/>
+      <c r="J92" t="s">
         <v>253</v>
       </c>
-      <c r="J92" s="4"/>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
-      <c r="N92" s="4">
-        <v>1</v>
-      </c>
+      <c r="N92" s="4"/>
       <c r="O92" s="4">
         <v>1</v>
       </c>
       <c r="P92" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="4">
         <v>0</v>
@@ -6255,9 +6323,12 @@
       <c r="S92" s="4">
         <v>0</v>
       </c>
-      <c r="T92" s="4"/>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T92" s="4">
+        <v>0</v>
+      </c>
+      <c r="U92" s="4"/>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
         <v>11</v>
       </c>
@@ -6278,21 +6349,19 @@
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
-      <c r="I93" t="s">
+      <c r="I93" s="4"/>
+      <c r="J93" t="s">
         <v>275</v>
       </c>
-      <c r="J93" s="4"/>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
-      <c r="N93" s="4">
-        <v>6</v>
-      </c>
+      <c r="N93" s="4"/>
       <c r="O93" s="4">
         <v>6</v>
       </c>
       <c r="P93" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q93" s="4">
         <v>0</v>
@@ -6303,9 +6372,12 @@
       <c r="S93" s="4">
         <v>0</v>
       </c>
-      <c r="T93" s="4"/>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T93" s="4">
+        <v>0</v>
+      </c>
+      <c r="U93" s="4"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>11</v>
       </c>
@@ -6326,21 +6398,19 @@
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
-      <c r="I94" t="s">
+      <c r="I94" s="4"/>
+      <c r="J94" t="s">
         <v>253</v>
       </c>
-      <c r="J94" s="4"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
-      <c r="N94" s="4">
-        <v>1</v>
-      </c>
+      <c r="N94" s="4"/>
       <c r="O94" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="4">
         <v>1</v>
@@ -6349,11 +6419,14 @@
         <v>1</v>
       </c>
       <c r="S94" s="4">
-        <v>0</v>
-      </c>
-      <c r="T94" s="4"/>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T94" s="4">
+        <v>0</v>
+      </c>
+      <c r="U94" s="4"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>11</v>
       </c>
@@ -6374,21 +6447,19 @@
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
-      <c r="I95" t="s">
+      <c r="I95" s="4"/>
+      <c r="J95" t="s">
         <v>253</v>
       </c>
-      <c r="J95" s="4"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
-      <c r="N95" s="4">
-        <v>1</v>
-      </c>
+      <c r="N95" s="4"/>
       <c r="O95" s="4">
         <v>1</v>
       </c>
       <c r="P95" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="4">
         <v>0</v>
@@ -6399,9 +6470,12 @@
       <c r="S95" s="4">
         <v>0</v>
       </c>
-      <c r="T95" s="4"/>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T95" s="4">
+        <v>0</v>
+      </c>
+      <c r="U95" s="4"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
         <v>11</v>
       </c>
@@ -6422,21 +6496,19 @@
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
-      <c r="I96" t="s">
+      <c r="I96" s="4"/>
+      <c r="J96" t="s">
         <v>272</v>
       </c>
-      <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
-      <c r="N96" s="4">
-        <v>5</v>
-      </c>
+      <c r="N96" s="4"/>
       <c r="O96" s="4">
         <v>5</v>
       </c>
       <c r="P96" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q96" s="4">
         <v>0</v>
@@ -6447,9 +6519,12 @@
       <c r="S96" s="4">
         <v>0</v>
       </c>
-      <c r="T96" s="4"/>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T96" s="4">
+        <v>0</v>
+      </c>
+      <c r="U96" s="4"/>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>11</v>
       </c>
@@ -6470,21 +6545,19 @@
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
-      <c r="I97" t="s">
+      <c r="I97" s="4"/>
+      <c r="J97" t="s">
         <v>155</v>
       </c>
-      <c r="J97" s="4"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
-      <c r="N97" s="4">
+      <c r="N97" s="4"/>
+      <c r="O97" s="4">
         <v>3</v>
       </c>
-      <c r="O97" s="4">
-        <v>0</v>
-      </c>
       <c r="P97" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="4">
         <v>1</v>
@@ -6493,11 +6566,14 @@
         <v>1</v>
       </c>
       <c r="S97" s="4">
-        <v>0</v>
-      </c>
-      <c r="T97" s="4"/>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T97" s="4">
+        <v>0</v>
+      </c>
+      <c r="U97" s="4"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>11</v>
       </c>
@@ -6518,21 +6594,19 @@
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
-      <c r="I98" t="s">
+      <c r="I98" s="4"/>
+      <c r="J98" t="s">
         <v>252</v>
       </c>
-      <c r="J98" s="4"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
-      <c r="N98" s="4">
-        <v>2</v>
-      </c>
+      <c r="N98" s="4"/>
       <c r="O98" s="4">
         <v>2</v>
       </c>
       <c r="P98" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q98" s="4">
         <v>0</v>
@@ -6543,9 +6617,12 @@
       <c r="S98" s="4">
         <v>0</v>
       </c>
-      <c r="T98" s="4"/>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T98" s="4">
+        <v>0</v>
+      </c>
+      <c r="U98" s="4"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
         <v>11</v>
       </c>
@@ -6566,21 +6643,19 @@
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
-      <c r="I99" t="s">
+      <c r="I99" s="4"/>
+      <c r="J99" t="s">
         <v>275</v>
       </c>
-      <c r="J99" s="4"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
-      <c r="N99" s="4">
-        <v>6</v>
-      </c>
+      <c r="N99" s="4"/>
       <c r="O99" s="4">
         <v>6</v>
       </c>
       <c r="P99" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q99" s="4">
         <v>0</v>
@@ -6591,9 +6666,12 @@
       <c r="S99" s="4">
         <v>0</v>
       </c>
-      <c r="T99" s="4"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T99" s="4">
+        <v>0</v>
+      </c>
+      <c r="U99" s="4"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>11</v>
       </c>
@@ -6614,21 +6692,19 @@
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
-      <c r="I100" t="s">
+      <c r="I100" s="4"/>
+      <c r="J100" t="s">
         <v>155</v>
       </c>
-      <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
-      <c r="N100" s="4">
+      <c r="N100" s="4"/>
+      <c r="O100" s="4">
         <v>3</v>
       </c>
-      <c r="O100" s="4">
-        <v>0</v>
-      </c>
       <c r="P100" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="4">
         <v>1</v>
@@ -6637,11 +6713,14 @@
         <v>1</v>
       </c>
       <c r="S100" s="4">
-        <v>0</v>
-      </c>
-      <c r="T100" s="4"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T100" s="4">
+        <v>0</v>
+      </c>
+      <c r="U100" s="4"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>11</v>
       </c>
@@ -6662,21 +6741,19 @@
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
-      <c r="I101" t="s">
+      <c r="I101" s="4"/>
+      <c r="J101" t="s">
         <v>253</v>
       </c>
-      <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
-      <c r="N101" s="4">
-        <v>1</v>
-      </c>
+      <c r="N101" s="4"/>
       <c r="O101" s="4">
         <v>1</v>
       </c>
       <c r="P101" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="4">
         <v>0</v>
@@ -6687,9 +6764,12 @@
       <c r="S101" s="4">
         <v>0</v>
       </c>
-      <c r="T101" s="4"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T101" s="4">
+        <v>0</v>
+      </c>
+      <c r="U101" s="4"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
         <v>11</v>
       </c>
@@ -6710,21 +6790,19 @@
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
-      <c r="I102" t="s">
+      <c r="I102" s="1"/>
+      <c r="J102" t="s">
         <v>253</v>
       </c>
-      <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
-      <c r="N102" s="1">
-        <v>1</v>
-      </c>
+      <c r="N102" s="1"/>
       <c r="O102" s="1">
         <v>1</v>
       </c>
       <c r="P102" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="1">
         <v>0</v>
@@ -6735,9 +6813,12 @@
       <c r="S102" s="1">
         <v>0</v>
       </c>
-      <c r="T102" s="1"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T102" s="1">
+        <v>0</v>
+      </c>
+      <c r="U102" s="1"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>11</v>
       </c>
@@ -6758,35 +6839,36 @@
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
-      <c r="I103" s="4" t="s">
+      <c r="I103" s="4"/>
+      <c r="J103" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="J103" s="4"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
-      <c r="N103" s="4">
+      <c r="N103" s="4"/>
+      <c r="O103" s="4">
         <f>TFO!J23</f>
         <v>62</v>
       </c>
-      <c r="O103" s="4">
-        <v>0</v>
-      </c>
       <c r="P103" s="4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="4">
         <v>21</v>
       </c>
       <c r="R103" s="4">
+        <v>21</v>
+      </c>
+      <c r="S103" s="4">
         <v>20</v>
       </c>
-      <c r="S103" s="4">
-        <v>0</v>
-      </c>
-      <c r="T103" s="4"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T103" s="4">
+        <v>0</v>
+      </c>
+      <c r="U103" s="4"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>11</v>
       </c>
@@ -6807,35 +6889,36 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="4" t="s">
+      <c r="I104" s="4"/>
+      <c r="J104" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
-      <c r="N104" s="4">
+      <c r="N104" s="4"/>
+      <c r="O104" s="4">
         <f>TFO!J24</f>
         <v>2</v>
       </c>
-      <c r="O104" s="4">
-        <v>0</v>
-      </c>
       <c r="P104" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q104" s="4">
         <v>1</v>
       </c>
       <c r="R104" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S104" s="4">
         <v>0</v>
       </c>
-      <c r="T104" s="4"/>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T104" s="4">
+        <v>0</v>
+      </c>
+      <c r="U104" s="4"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>11</v>
       </c>
@@ -6856,22 +6939,20 @@
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="4" t="s">
+      <c r="I105" s="4"/>
+      <c r="J105" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
-      <c r="N105" s="4">
+      <c r="N105" s="4"/>
+      <c r="O105" s="4">
         <f>TFO!J25</f>
         <v>33</v>
       </c>
-      <c r="O105" s="4">
-        <v>0</v>
-      </c>
       <c r="P105" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="4">
         <v>12</v>
@@ -6880,11 +6961,14 @@
         <v>12</v>
       </c>
       <c r="S105" s="4">
-        <v>0</v>
-      </c>
-      <c r="T105" s="4"/>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="T105" s="4">
+        <v>0</v>
+      </c>
+      <c r="U105" s="4"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>11</v>
       </c>
@@ -6905,22 +6989,20 @@
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
-      <c r="I106" s="4" t="s">
+      <c r="I106" s="4"/>
+      <c r="J106" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="J106" s="4"/>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
-      <c r="N106" s="4">
+      <c r="N106" s="4"/>
+      <c r="O106" s="4">
         <f>TFO!J26</f>
         <v>51</v>
       </c>
-      <c r="O106" s="4">
-        <v>0</v>
-      </c>
       <c r="P106" s="4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q106" s="4">
         <v>17</v>
@@ -6929,11 +7011,14 @@
         <v>17</v>
       </c>
       <c r="S106" s="4">
-        <v>0</v>
-      </c>
-      <c r="T106" s="4"/>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="T106" s="4">
+        <v>0</v>
+      </c>
+      <c r="U106" s="4"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>11</v>
       </c>
@@ -6954,22 +7039,20 @@
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
-      <c r="I107" t="s">
+      <c r="I107" s="4"/>
+      <c r="J107" t="s">
         <v>147</v>
       </c>
-      <c r="J107" s="4"/>
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
-      <c r="N107" s="4">
+      <c r="N107" s="4"/>
+      <c r="O107" s="4">
         <f>TFO!J27</f>
         <v>6</v>
       </c>
-      <c r="O107" s="4">
-        <v>0</v>
-      </c>
       <c r="P107" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="4">
         <v>2</v>
@@ -6978,11 +7061,14 @@
         <v>2</v>
       </c>
       <c r="S107" s="4">
-        <v>0</v>
-      </c>
-      <c r="T107" s="4"/>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T107" s="4">
+        <v>0</v>
+      </c>
+      <c r="U107" s="4"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
         <v>11</v>
       </c>
@@ -7003,22 +7089,20 @@
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
-      <c r="I108" t="s">
+      <c r="I108" s="4"/>
+      <c r="J108" t="s">
         <v>147</v>
       </c>
-      <c r="J108" s="4"/>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
-      <c r="N108" s="4">
+      <c r="N108" s="4"/>
+      <c r="O108" s="4">
         <f>TFO!J28</f>
         <v>6</v>
       </c>
-      <c r="O108" s="4">
-        <v>0</v>
-      </c>
       <c r="P108" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q108" s="4">
         <v>2</v>
@@ -7027,11 +7111,14 @@
         <v>2</v>
       </c>
       <c r="S108" s="4">
-        <v>0</v>
-      </c>
-      <c r="T108" s="4"/>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T108" s="4">
+        <v>0</v>
+      </c>
+      <c r="U108" s="4"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>11</v>
       </c>
@@ -7052,22 +7139,20 @@
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
-      <c r="I109" t="s">
+      <c r="I109" s="4"/>
+      <c r="J109" t="s">
         <v>155</v>
       </c>
-      <c r="J109" s="4"/>
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
-      <c r="N109" s="4">
+      <c r="N109" s="4"/>
+      <c r="O109" s="4">
         <f>TFO!J29</f>
         <v>3</v>
       </c>
-      <c r="O109" s="4">
-        <v>0</v>
-      </c>
       <c r="P109" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="4">
         <v>1</v>
@@ -7076,11 +7161,14 @@
         <v>1</v>
       </c>
       <c r="S109" s="4">
-        <v>0</v>
-      </c>
-      <c r="T109" s="4"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T109" s="4">
+        <v>0</v>
+      </c>
+      <c r="U109" s="4"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>11</v>
       </c>
@@ -7101,22 +7189,20 @@
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
-      <c r="I110" t="s">
+      <c r="I110" s="4"/>
+      <c r="J110" t="s">
         <v>155</v>
       </c>
-      <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
-      <c r="N110" s="4">
+      <c r="N110" s="4"/>
+      <c r="O110" s="4">
         <f>TFO!J30</f>
         <v>3</v>
       </c>
-      <c r="O110" s="4">
-        <v>0</v>
-      </c>
       <c r="P110" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="4">
         <v>1</v>
@@ -7125,11 +7211,14 @@
         <v>1</v>
       </c>
       <c r="S110" s="4">
-        <v>0</v>
-      </c>
-      <c r="T110" s="4"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T110" s="4">
+        <v>0</v>
+      </c>
+      <c r="U110" s="4"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
         <v>11</v>
       </c>
@@ -7150,22 +7239,20 @@
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
-      <c r="I111" t="s">
+      <c r="I111" s="4"/>
+      <c r="J111" t="s">
         <v>147</v>
       </c>
-      <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
-      <c r="N111" s="4">
+      <c r="N111" s="4"/>
+      <c r="O111" s="4">
         <f>TFO!J31</f>
         <v>6</v>
       </c>
-      <c r="O111" s="4">
-        <v>0</v>
-      </c>
       <c r="P111" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q111" s="4">
         <v>2</v>
@@ -7174,11 +7261,14 @@
         <v>2</v>
       </c>
       <c r="S111" s="4">
-        <v>0</v>
-      </c>
-      <c r="T111" s="4"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="T111" s="4">
+        <v>0</v>
+      </c>
+      <c r="U111" s="4"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>11</v>
       </c>
@@ -7197,22 +7287,20 @@
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
-      <c r="I112" t="s">
+      <c r="I112" s="4"/>
+      <c r="J112" t="s">
         <v>155</v>
       </c>
-      <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
-      <c r="N112" s="4">
+      <c r="N112" s="4"/>
+      <c r="O112" s="4">
         <f>TFO!J32</f>
         <v>3</v>
       </c>
-      <c r="O112" s="4">
-        <v>0</v>
-      </c>
       <c r="P112" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="4">
         <v>1</v>
@@ -7221,11 +7309,14 @@
         <v>1</v>
       </c>
       <c r="S112" s="4">
-        <v>0</v>
-      </c>
-      <c r="T112" s="4"/>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="T112" s="4">
+        <v>0</v>
+      </c>
+      <c r="U112" s="4"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>11</v>
       </c>
@@ -7244,22 +7335,20 @@
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
-      <c r="I113" t="s">
+      <c r="I113" s="4"/>
+      <c r="J113" t="s">
         <v>253</v>
       </c>
-      <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
-      <c r="N113" s="4">
+      <c r="N113" s="4"/>
+      <c r="O113" s="4">
         <f>TFO!J33</f>
         <v>1</v>
       </c>
-      <c r="O113" s="4">
-        <v>1</v>
-      </c>
       <c r="P113" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="4">
         <v>0</v>
@@ -7270,9 +7359,12 @@
       <c r="S113" s="4">
         <v>0</v>
       </c>
-      <c r="T113" s="4"/>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T113" s="4">
+        <v>0</v>
+      </c>
+      <c r="U113" s="4"/>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
         <v>11</v>
       </c>
@@ -7291,22 +7383,20 @@
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
-      <c r="I114" t="s">
+      <c r="I114" s="4"/>
+      <c r="J114" t="s">
         <v>140</v>
       </c>
-      <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
-      <c r="N114" s="4">
+      <c r="N114" s="4"/>
+      <c r="O114" s="4">
         <f>TFO!J34</f>
         <v>12</v>
       </c>
-      <c r="O114" s="4">
-        <v>0</v>
-      </c>
       <c r="P114" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="4">
         <v>4</v>
@@ -7315,11 +7405,14 @@
         <v>4</v>
       </c>
       <c r="S114" s="4">
-        <v>0</v>
-      </c>
-      <c r="T114" s="4"/>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="T114" s="4">
+        <v>0</v>
+      </c>
+      <c r="U114" s="4"/>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>11</v>
       </c>
@@ -7340,20 +7433,18 @@
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
-      <c r="I115" t="s">
+      <c r="I115" s="4"/>
+      <c r="J115" t="s">
         <v>271</v>
       </c>
-      <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
-      <c r="N115" s="4">
+      <c r="N115" s="4"/>
+      <c r="O115" s="4">
         <f>TFO!J35</f>
         <v>0</v>
       </c>
-      <c r="O115" s="4">
-        <v>0</v>
-      </c>
       <c r="P115" s="4">
         <v>0</v>
       </c>
@@ -7366,9 +7457,12 @@
       <c r="S115" s="4">
         <v>0</v>
       </c>
-      <c r="T115" s="4"/>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T115" s="4">
+        <v>0</v>
+      </c>
+      <c r="U115" s="4"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>11</v>
       </c>
@@ -7389,22 +7483,20 @@
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
-      <c r="I116" t="s">
+      <c r="I116" s="4"/>
+      <c r="J116" t="s">
         <v>253</v>
       </c>
-      <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
-      <c r="N116" s="4">
+      <c r="N116" s="4"/>
+      <c r="O116" s="4">
         <f>TFO!J36</f>
         <v>1</v>
       </c>
-      <c r="O116" s="4">
-        <v>1</v>
-      </c>
       <c r="P116" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="4">
         <v>0</v>
@@ -7415,9 +7507,12 @@
       <c r="S116" s="4">
         <v>0</v>
       </c>
-      <c r="T116" s="4"/>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T116" s="4">
+        <v>0</v>
+      </c>
+      <c r="U116" s="4"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
         <v>11</v>
       </c>
@@ -7438,22 +7533,20 @@
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
-      <c r="I117" t="s">
+      <c r="I117" s="4"/>
+      <c r="J117" t="s">
         <v>147</v>
       </c>
-      <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
-      <c r="N117" s="4">
+      <c r="N117" s="4"/>
+      <c r="O117" s="4">
         <f>TFO!J37</f>
         <v>6</v>
       </c>
-      <c r="O117" s="4">
-        <v>0</v>
-      </c>
       <c r="P117" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="4">
         <v>2</v>
@@ -7462,9 +7555,12 @@
         <v>2</v>
       </c>
       <c r="S117" s="4">
-        <v>0</v>
-      </c>
-      <c r="T117" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="T117" s="4">
+        <v>0</v>
+      </c>
+      <c r="U117" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -7478,35 +7574,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6343EE0-D320-4977-9825-4200D3368BED}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.41796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3125" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="8.3125" customWidth="1"/>
+    <col min="5" max="5" width="19.41796875" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.3125" customWidth="1"/>
     <col min="8" max="8" width="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="46.6640625" customWidth="1"/>
-    <col min="10" max="10" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.33203125" customWidth="1"/>
-    <col min="12" max="12" width="34.6640625" customWidth="1"/>
-    <col min="13" max="13" width="23.21875" customWidth="1"/>
-    <col min="14" max="14" width="34.88671875" customWidth="1"/>
-    <col min="15" max="15" width="26.77734375" customWidth="1"/>
-    <col min="16" max="16" width="39.33203125" customWidth="1"/>
-    <col min="17" max="17" width="13.77734375" customWidth="1"/>
-    <col min="18" max="18" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="45.109375" customWidth="1"/>
-    <col min="20" max="20" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="49.88671875" customWidth="1"/>
-    <col min="22" max="22" width="25.109375" customWidth="1"/>
+    <col min="9" max="9" width="46.68359375" customWidth="1"/>
+    <col min="10" max="10" width="43.3125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.3125" customWidth="1"/>
+    <col min="12" max="12" width="34.68359375" customWidth="1"/>
+    <col min="13" max="13" width="23.20703125" customWidth="1"/>
+    <col min="14" max="14" width="34.89453125" customWidth="1"/>
+    <col min="15" max="15" width="26.7890625" customWidth="1"/>
+    <col min="16" max="16" width="39.3125" customWidth="1"/>
+    <col min="17" max="17" width="13.7890625" customWidth="1"/>
+    <col min="18" max="18" width="33.41796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="45.1015625" customWidth="1"/>
+    <col min="20" max="20" width="40.41796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="49.89453125" customWidth="1"/>
+    <col min="22" max="22" width="25.1015625" customWidth="1"/>
     <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="15.5546875" customWidth="1"/>
+    <col min="24" max="24" width="15.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>196</v>
       </c>
@@ -7580,7 +7676,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>218</v>
       </c>
@@ -7661,7 +7757,7 @@
         <v>2.5516553150693633</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>218</v>
       </c>
@@ -7718,7 +7814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>222</v>
       </c>
@@ -7783,7 +7879,7 @@
         <v>0.42808153681559535</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>224</v>
       </c>
@@ -7848,7 +7944,7 @@
         <v>2.7111830664987711</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>225</v>
       </c>
@@ -7913,7 +8009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -7978,7 +8074,7 @@
         <v>0.18992832745236415</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>227</v>
       </c>
@@ -8043,7 +8139,7 @@
         <v>0.40861677010253639</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>228</v>
       </c>
@@ -8108,7 +8204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>228</v>
       </c>
@@ -8173,7 +8269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>230</v>
       </c>
@@ -8238,7 +8334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>231</v>
       </c>
@@ -8303,7 +8399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>232</v>
       </c>
@@ -8368,7 +8464,7 @@
         <v>0.70165756054775441</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>233</v>
       </c>
@@ -8433,7 +8529,7 @@
         <v>1.2948798803565318</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>234</v>
       </c>
@@ -8498,7 +8594,7 @@
         <v>0.77291166383862875</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>235</v>
       </c>
@@ -8563,7 +8659,7 @@
         <v>1.1040147594260059</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>236</v>
       </c>
@@ -8628,7 +8724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>237</v>
       </c>
@@ -8693,7 +8789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>238</v>
       </c>
@@ -8761,7 +8857,7 @@
         <v>0.118974377457405</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -8814,7 +8910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -8859,7 +8955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -8904,7 +9000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -8949,7 +9045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -8994,7 +9090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -9039,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -9084,7 +9180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -9129,7 +9225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -9174,7 +9270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -9219,7 +9315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -9261,7 +9357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -9303,7 +9399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -9345,7 +9441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -9390,7 +9486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -9435,7 +9531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>11</v>
       </c>

--- a/input/Spinning.xlsx
+++ b/input/Spinning.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://welspungroup-my.sharepoint.com/personal/sahith_thadimudupula_welspun_com/Documents/Desktop/Manning_FInal_sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://welspungroup-my.sharepoint.com/personal/sahith_thadimudupula_welspun_com/Documents/Desktop/spinning/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{A27A5A94-B1FD-49F2-9F70-8465DE6A863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E476F20-40BC-4B9D-8573-7B5DC7559817}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A27A5A94-B1FD-49F2-9F70-8465DE6A863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D66C447-DD62-4CCB-9BE1-17F8B0E9B344}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="TFO" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spinning!$A$1:$U$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spinning!$A$1:$T$117</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="286">
   <si>
     <t>Location</t>
   </si>
@@ -893,9 +893,6 @@
   </si>
   <si>
     <t>Dept_Machine_Name</t>
-  </si>
-  <si>
-    <t>Manpower_Base_Qty</t>
   </si>
 </sst>
 </file>
@@ -959,26 +956,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="31">
     <dxf>
       <font>
         <b val="0"/>
@@ -1390,30 +1368,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}" name="Table1" displayName="Table1" ref="A1:U117" totalsRowShown="0" dataDxfId="21">
-  <autoFilter ref="A1:U117" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}"/>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{85A1F019-9DB7-48AC-AF2B-F0C9FBE637DA}" name="Location" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{545588E2-5E30-4A62-AB93-1DBC57F6BCF8}" name="Business" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{44C3C497-13A6-40FF-AABF-EC930E13E039}" name="Section" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{ED8F8366-2CFD-45B1-B1C2-AA92F55B23F6}" name="Sr_No" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{3C440E90-56BF-4BC4-ACD0-A73E98969A14}" name="Dept_Machine_Name" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{EADE3DD8-7C1C-4874-8032-AD8F2F81A125}" name="Designation" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{292F7B89-A9FA-4B1D-8581-9D4596E679FF}" name="Machine_Count" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{C464261F-9918-428A-92D8-8AA20D507764}" name="Manpower_Base_Qty" dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{090D3B71-C4CF-432F-B817-104F30316591}" name="Workload" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{9EDB9484-B177-478C-9BA3-4C1AE3030F95}" name="Formulas" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{3A1186F6-9294-4AEC-A543-A07372ADEF4D}" name="BE_Scientific_Manpower" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}" name="Table1" displayName="Table1" ref="A1:T117" totalsRowShown="0" dataDxfId="20">
+  <autoFilter ref="A1:T117" xr:uid="{F622A60C-E8BF-4683-BFA8-DC9CDCD99FD8}"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{85A1F019-9DB7-48AC-AF2B-F0C9FBE637DA}" name="Location" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{545588E2-5E30-4A62-AB93-1DBC57F6BCF8}" name="Business" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{44C3C497-13A6-40FF-AABF-EC930E13E039}" name="Section" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{ED8F8366-2CFD-45B1-B1C2-AA92F55B23F6}" name="Sr_No" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{3C440E90-56BF-4BC4-ACD0-A73E98969A14}" name="Dept_Machine_Name" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{EADE3DD8-7C1C-4874-8032-AD8F2F81A125}" name="Designation" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{292F7B89-A9FA-4B1D-8581-9D4596E679FF}" name="Machine_Count" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{090D3B71-C4CF-432F-B817-104F30316591}" name="Workload" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{9EDB9484-B177-478C-9BA3-4C1AE3030F95}" name="Formulas" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{3A1186F6-9294-4AEC-A543-A07372ADEF4D}" name="BE_Scientific_Manpower" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{071CCBE0-65D5-467E-AFCC-8949549E1BB6}" name="Operator_Type" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{F5544431-B0F5-4C79-B5EB-61614939F4B5}" name="Contractors" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{15BE4AF0-E211-4DE0-800A-0EDB9C705B37}" name="Company_Associate" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{47E45710-4EB9-4699-B8AD-09AC38DE8C54}" name="BE_Final_Manpower" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{38203A5B-662C-436E-A752-C238B552EF03}" name="General_Shift" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{3D149A8F-3122-4C7E-B50D-02B6DF1691E0}" name="Shift_A" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{0AFA7034-EEDB-4D14-A601-C01016D3A7D5}" name="Shift_B" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{64D43A66-597F-4C18-84E0-E76FCB0F95CC}" name="Shift_C" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{554EDC51-4B6D-44FF-BB2C-DA6797B32110}" name="Reliever" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{FF4E975E-F83C-4D1D-8950-072C414D6E58}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1444,18 +1421,18 @@
       <calculatedColumnFormula>L2/I2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{7C882653-B2FB-4460-945F-BEC827034FAE}" name="formula_No. of TFO Required/ shift "/>
-    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="14" xr3:uid="{74DD064C-08DB-4132-A242-1290AD15CDB8}" name="No. of TFO Required/ shift " dataDxfId="30" totalsRowDxfId="29"/>
     <tableColumn id="15" xr3:uid="{65F3003E-C476-4D6D-BE1A-6488E17CDB9D}" name="mpm"/>
-    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{6E9D763E-DE2C-4A86-B1EA-5287AC19467B}" name="Eff" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{4C4EE216-BFC8-45EA-BA92-DA7C3E734438}" name="Formula_kgs/drum/day " dataDxfId="26" totalsRowDxfId="25"/>
     <tableColumn id="18" xr3:uid="{00170897-62B8-4C84-AE04-5EAE44ABC362}" name="kgs/drum/day ">
       <calculatedColumnFormula>Q2*R2*8*60*1.09/(C2*840*2.202)*3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{2DD7DB04-94B4-4773-9E4C-D99D0E582A8C}" name="formula_No. of Drums"/>
-    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="25" totalsRowDxfId="24">
+    <tableColumn id="20" xr3:uid="{B964DFB3-EA94-419A-8A86-F1F5917ADCA3}" name="No. of Drums " dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>L2/T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="21" xr3:uid="{ACA15BF8-B0A7-481E-A7F2-D7E94E5D9CB0}" name="formula_no. of machines" dataDxfId="22" totalsRowDxfId="21"/>
     <tableColumn id="22" xr3:uid="{0459E32F-2AB6-434A-9439-F5F08B7C6254}" name="no. of machines">
       <calculatedColumnFormula>V2/72</calculatedColumnFormula>
     </tableColumn>
@@ -1749,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U117"/>
+  <dimension ref="A1:T117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13.1015625" customWidth="1"/>
@@ -1759,18 +1736,17 @@
     <col min="5" max="5" width="46.7890625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.41796875" customWidth="1"/>
     <col min="7" max="7" width="20.7890625" customWidth="1"/>
-    <col min="8" max="8" width="23.1015625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.41796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="31.5234375" customWidth="1"/>
-    <col min="15" max="15" width="26.20703125" customWidth="1"/>
-    <col min="16" max="16" width="18.7890625" customWidth="1"/>
-    <col min="17" max="19" width="11.5234375" customWidth="1"/>
-    <col min="20" max="20" width="12.3125" customWidth="1"/>
-    <col min="21" max="21" width="38.68359375" customWidth="1"/>
+    <col min="8" max="8" width="48.41796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="31.5234375" customWidth="1"/>
+    <col min="14" max="14" width="26.20703125" customWidth="1"/>
+    <col min="15" max="15" width="18.7890625" customWidth="1"/>
+    <col min="16" max="18" width="11.5234375" customWidth="1"/>
+    <col min="19" max="19" width="12.3125" customWidth="1"/>
+    <col min="20" max="20" width="38.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1793,49 +1769,46 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>286</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s">
-        <v>45</v>
+        <v>270</v>
       </c>
       <c r="K1" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="L1" t="s">
-        <v>284</v>
+        <v>42</v>
       </c>
       <c r="M1" t="s">
-        <v>42</v>
+        <v>283</v>
       </c>
       <c r="N1" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="O1" t="s">
-        <v>269</v>
+        <v>5</v>
       </c>
       <c r="P1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T1" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1857,20 +1830,23 @@
       <c r="G2">
         <v>8</v>
       </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
       <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
         <v>46</v>
       </c>
-      <c r="K2">
-        <v>12</v>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="N2">
+        <v>9</v>
       </c>
       <c r="O2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -1879,16 +1855,13 @@
         <v>3</v>
       </c>
       <c r="S2">
-        <v>3</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1910,20 +1883,23 @@
       <c r="G3">
         <v>52</v>
       </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
       <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
         <v>47</v>
       </c>
-      <c r="K3">
+      <c r="J3">
         <v>7.09</v>
       </c>
+      <c r="N3">
+        <v>9</v>
+      </c>
       <c r="O3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3">
         <v>3</v>
@@ -1932,13 +1908,10 @@
         <v>3</v>
       </c>
       <c r="S3">
-        <v>3</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1960,20 +1933,23 @@
       <c r="G4">
         <v>9</v>
       </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
       <c r="I4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" t="s">
         <v>48</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>3</v>
       </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
       <c r="O4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1982,13 +1958,10 @@
         <v>1</v>
       </c>
       <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2010,20 +1983,23 @@
       <c r="G5">
         <v>22</v>
       </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
       <c r="I5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="K5">
+      <c r="J5">
         <v>16.5</v>
       </c>
+      <c r="N5">
+        <v>18</v>
+      </c>
       <c r="O5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>6</v>
@@ -2032,13 +2008,10 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>6</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2060,20 +2033,23 @@
       <c r="G6">
         <v>4</v>
       </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
       <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s">
         <v>50</v>
       </c>
-      <c r="K6">
+      <c r="J6">
         <v>3</v>
       </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
       <c r="O6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -2082,13 +2058,10 @@
         <v>1</v>
       </c>
       <c r="S6">
-        <v>1</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2110,20 +2083,23 @@
       <c r="G7">
         <v>3</v>
       </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
       <c r="I7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" t="s">
         <v>51</v>
       </c>
-      <c r="K7">
+      <c r="J7">
         <v>4.5</v>
       </c>
+      <c r="N7">
+        <v>6</v>
+      </c>
       <c r="O7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -2132,13 +2108,10 @@
         <v>2</v>
       </c>
       <c r="S7">
-        <v>2</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2160,20 +2133,23 @@
       <c r="G8">
         <v>18</v>
       </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
       <c r="I8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" t="s">
         <v>52</v>
       </c>
-      <c r="K8">
+      <c r="J8">
         <v>5.4</v>
       </c>
+      <c r="N8">
+        <v>6</v>
+      </c>
       <c r="O8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2182,13 +2158,10 @@
         <v>2</v>
       </c>
       <c r="S8">
-        <v>2</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2210,20 +2183,23 @@
       <c r="G9">
         <v>21</v>
       </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
       <c r="I9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" t="s">
         <v>53</v>
       </c>
-      <c r="K9">
+      <c r="J9">
         <v>15.75</v>
       </c>
+      <c r="N9">
+        <v>15</v>
+      </c>
       <c r="O9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -2232,13 +2208,10 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>5</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2260,17 +2233,20 @@
       <c r="G10">
         <v>5</v>
       </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
       <c r="I10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" t="s">
         <v>54</v>
       </c>
-      <c r="K10">
+      <c r="J10">
         <v>3.75</v>
       </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
       <c r="O10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -2282,13 +2258,10 @@
         <v>1</v>
       </c>
       <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2310,20 +2283,23 @@
       <c r="G11">
         <v>16</v>
       </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
       <c r="I11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" t="s">
         <v>55</v>
       </c>
-      <c r="K11">
+      <c r="J11">
         <v>24</v>
       </c>
+      <c r="N11">
+        <v>27</v>
+      </c>
       <c r="O11">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -2332,16 +2308,13 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>9</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2363,20 +2336,23 @@
       <c r="G12">
         <v>16</v>
       </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
       <c r="I12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" t="s">
         <v>55</v>
       </c>
-      <c r="K12">
+      <c r="J12">
         <v>24</v>
       </c>
+      <c r="N12">
+        <v>27</v>
+      </c>
       <c r="O12">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -2385,13 +2361,10 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>9</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2410,20 +2383,23 @@
       <c r="F13" t="s">
         <v>28</v>
       </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
       <c r="I13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" t="s">
         <v>155</v>
       </c>
-      <c r="K13">
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="N13">
         <v>3</v>
       </c>
       <c r="O13">
         <v>3</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2434,11 +2410,8 @@
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2457,20 +2430,23 @@
       <c r="F14" t="s">
         <v>29</v>
       </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
       <c r="I14" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" t="s">
         <v>147</v>
       </c>
-      <c r="K14">
+      <c r="J14">
         <v>6</v>
       </c>
+      <c r="N14">
+        <v>6</v>
+      </c>
       <c r="O14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -2479,13 +2455,10 @@
         <v>2</v>
       </c>
       <c r="S14">
-        <v>2</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2504,20 +2477,23 @@
       <c r="F15" t="s">
         <v>31</v>
       </c>
+      <c r="H15" t="s">
+        <v>42</v>
+      </c>
       <c r="I15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" t="s">
         <v>147</v>
       </c>
-      <c r="K15">
+      <c r="J15">
         <v>6</v>
       </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
       <c r="O15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15">
         <v>2</v>
@@ -2526,13 +2502,10 @@
         <v>2</v>
       </c>
       <c r="S15">
-        <v>2</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2551,13 +2524,16 @@
       <c r="F16" t="s">
         <v>15</v>
       </c>
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
       <c r="I16" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" t="s">
         <v>271</v>
       </c>
-      <c r="K16">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
       <c r="O16">
@@ -2575,14 +2551,11 @@
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16" t="s">
+      <c r="T16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2604,20 +2577,23 @@
       <c r="G17">
         <v>7</v>
       </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
       <c r="I17" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" t="s">
         <v>59</v>
       </c>
-      <c r="K17">
+      <c r="J17">
         <v>30</v>
       </c>
+      <c r="N17">
+        <v>30</v>
+      </c>
       <c r="O17">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2626,13 +2602,10 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>10</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2654,20 +2627,23 @@
       <c r="G18">
         <v>12</v>
       </c>
+      <c r="H18" t="s">
+        <v>98</v>
+      </c>
       <c r="I18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J18" t="s">
         <v>61</v>
       </c>
-      <c r="K18">
+      <c r="J18">
         <v>25</v>
       </c>
+      <c r="N18">
+        <v>25</v>
+      </c>
       <c r="O18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>8</v>
@@ -2676,13 +2652,10 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>8</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2704,20 +2677,23 @@
       <c r="G19">
         <v>18</v>
       </c>
+      <c r="H19" t="s">
+        <v>98</v>
+      </c>
       <c r="I19" t="s">
-        <v>98</v>
-      </c>
-      <c r="J19" t="s">
         <v>63</v>
       </c>
-      <c r="K19">
+      <c r="J19">
         <v>54</v>
       </c>
+      <c r="N19">
+        <v>54</v>
+      </c>
       <c r="O19">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q19">
         <v>18</v>
@@ -2726,13 +2702,10 @@
         <v>18</v>
       </c>
       <c r="S19">
-        <v>18</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2754,20 +2727,23 @@
       <c r="G20">
         <v>4</v>
       </c>
+      <c r="H20" t="s">
+        <v>99</v>
+      </c>
       <c r="I20" t="s">
-        <v>99</v>
-      </c>
-      <c r="J20" t="s">
         <v>65</v>
       </c>
-      <c r="K20">
+      <c r="J20">
+        <v>12</v>
+      </c>
+      <c r="N20">
         <v>12</v>
       </c>
       <c r="O20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q20">
         <v>4</v>
@@ -2776,13 +2752,10 @@
         <v>4</v>
       </c>
       <c r="S20">
-        <v>4</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2801,20 +2774,23 @@
       <c r="F21" t="s">
         <v>15</v>
       </c>
+      <c r="H21" t="s">
+        <v>67</v>
+      </c>
       <c r="I21" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" t="s">
         <v>68</v>
       </c>
-      <c r="K21">
+      <c r="J21">
         <v>18</v>
       </c>
+      <c r="N21">
+        <v>18</v>
+      </c>
       <c r="O21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -2823,13 +2799,10 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>6</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2848,39 +2821,35 @@
       <c r="F22" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22">
-        <v>52608</v>
+      <c r="H22" t="s">
+        <v>70</v>
       </c>
       <c r="I22" t="s">
-        <v>70</v>
-      </c>
-      <c r="J22" t="s">
         <v>71</v>
       </c>
-      <c r="K22">
+      <c r="J22">
         <v>41</v>
       </c>
+      <c r="N22">
+        <v>41</v>
+      </c>
       <c r="O22">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q22">
         <v>14</v>
       </c>
       <c r="R22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S22">
-        <v>13</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -2902,20 +2871,23 @@
       <c r="G23">
         <v>7</v>
       </c>
+      <c r="H23" t="s">
+        <v>73</v>
+      </c>
       <c r="I23" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" t="s">
         <v>74</v>
       </c>
-      <c r="K23">
+      <c r="J23">
         <v>6</v>
       </c>
+      <c r="N23">
+        <v>6</v>
+      </c>
       <c r="O23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23">
         <v>2</v>
@@ -2924,13 +2896,10 @@
         <v>2</v>
       </c>
       <c r="S23">
-        <v>2</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2952,20 +2921,23 @@
       <c r="G24">
         <v>12</v>
       </c>
+      <c r="H24" t="s">
+        <v>76</v>
+      </c>
       <c r="I24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J24" t="s">
         <v>77</v>
       </c>
-      <c r="K24">
+      <c r="J24">
         <v>6</v>
       </c>
+      <c r="N24">
+        <v>6</v>
+      </c>
       <c r="O24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24">
         <v>2</v>
@@ -2974,13 +2946,10 @@
         <v>2</v>
       </c>
       <c r="S24">
-        <v>2</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3002,20 +2971,23 @@
       <c r="G25">
         <v>18</v>
       </c>
+      <c r="H25" t="s">
+        <v>79</v>
+      </c>
       <c r="I25" t="s">
-        <v>79</v>
-      </c>
-      <c r="J25" t="s">
         <v>80</v>
       </c>
-      <c r="K25">
+      <c r="J25">
+        <v>12</v>
+      </c>
+      <c r="N25">
         <v>12</v>
       </c>
       <c r="O25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -3024,13 +2996,10 @@
         <v>4</v>
       </c>
       <c r="S25">
-        <v>4</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3052,20 +3021,23 @@
       <c r="G26">
         <v>4</v>
       </c>
+      <c r="H26" t="s">
+        <v>82</v>
+      </c>
       <c r="I26" t="s">
-        <v>82</v>
-      </c>
-      <c r="J26" t="s">
         <v>83</v>
       </c>
-      <c r="K26">
+      <c r="J26">
         <v>3</v>
       </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
       <c r="O26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26">
         <v>1</v>
@@ -3074,13 +3046,10 @@
         <v>1</v>
       </c>
       <c r="S26">
-        <v>1</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3099,17 +3068,20 @@
       <c r="F27" t="s">
         <v>84</v>
       </c>
-      <c r="J27" t="s">
+      <c r="I27" t="s">
         <v>169</v>
       </c>
-      <c r="K27">
+      <c r="J27">
         <v>9</v>
       </c>
+      <c r="N27">
+        <v>9</v>
+      </c>
       <c r="O27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -3118,16 +3090,13 @@
         <v>3</v>
       </c>
       <c r="S27">
-        <v>3</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27" t="s">
+        <v>0</v>
+      </c>
+      <c r="T27" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3146,21 +3115,20 @@
       <c r="F28" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28">
-        <v>52608</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="I28" t="s">
         <v>147</v>
       </c>
-      <c r="K28">
+      <c r="J28">
         <v>6</v>
       </c>
+      <c r="N28">
+        <v>6</v>
+      </c>
       <c r="O28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28">
         <v>2</v>
@@ -3169,16 +3137,13 @@
         <v>2</v>
       </c>
       <c r="S28">
-        <v>2</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28" t="s">
+        <v>0</v>
+      </c>
+      <c r="T28" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3197,17 +3162,20 @@
       <c r="F29" t="s">
         <v>88</v>
       </c>
-      <c r="J29" t="s">
+      <c r="I29" t="s">
         <v>147</v>
       </c>
-      <c r="K29">
+      <c r="J29">
         <v>6</v>
       </c>
+      <c r="N29">
+        <v>6</v>
+      </c>
       <c r="O29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -3216,16 +3184,13 @@
         <v>2</v>
       </c>
       <c r="S29">
-        <v>2</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29" t="s">
+        <v>0</v>
+      </c>
+      <c r="T29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3244,17 +3209,20 @@
       <c r="F30" t="s">
         <v>42</v>
       </c>
-      <c r="J30" t="s">
+      <c r="I30" t="s">
         <v>147</v>
       </c>
-      <c r="K30">
+      <c r="J30">
         <v>6</v>
       </c>
+      <c r="N30">
+        <v>6</v>
+      </c>
       <c r="O30">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -3263,16 +3231,13 @@
         <v>2</v>
       </c>
       <c r="S30">
-        <v>2</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30" t="s">
+        <v>0</v>
+      </c>
+      <c r="T30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3291,17 +3256,20 @@
       <c r="F31" t="s">
         <v>42</v>
       </c>
-      <c r="J31" t="s">
+      <c r="I31" t="s">
         <v>147</v>
       </c>
-      <c r="K31">
+      <c r="J31">
         <v>6</v>
       </c>
+      <c r="N31">
+        <v>6</v>
+      </c>
       <c r="O31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31">
         <v>2</v>
@@ -3310,16 +3278,13 @@
         <v>2</v>
       </c>
       <c r="S31">
-        <v>2</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31" t="s">
+        <v>0</v>
+      </c>
+      <c r="T31" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3335,20 +3300,23 @@
       <c r="E32" t="s">
         <v>91</v>
       </c>
+      <c r="H32" t="s">
+        <v>92</v>
+      </c>
       <c r="I32" t="s">
-        <v>92</v>
-      </c>
-      <c r="J32" t="s">
         <v>147</v>
       </c>
-      <c r="K32">
+      <c r="J32">
         <v>6</v>
       </c>
+      <c r="N32">
+        <v>6</v>
+      </c>
       <c r="O32">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32">
         <v>2</v>
@@ -3357,16 +3325,13 @@
         <v>2</v>
       </c>
       <c r="S32">
-        <v>2</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32" t="s">
+        <v>0</v>
+      </c>
+      <c r="T32" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -3382,20 +3347,23 @@
       <c r="E33" t="s">
         <v>93</v>
       </c>
+      <c r="H33" t="s">
+        <v>94</v>
+      </c>
       <c r="I33" t="s">
-        <v>94</v>
-      </c>
-      <c r="J33" t="s">
         <v>147</v>
       </c>
-      <c r="K33">
+      <c r="J33">
         <v>6</v>
       </c>
+      <c r="N33">
+        <v>6</v>
+      </c>
       <c r="O33">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33">
         <v>2</v>
@@ -3404,16 +3372,13 @@
         <v>2</v>
       </c>
       <c r="S33">
-        <v>2</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33" t="s">
+        <v>0</v>
+      </c>
+      <c r="T33" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3429,20 +3394,23 @@
       <c r="E34" t="s">
         <v>95</v>
       </c>
+      <c r="H34" t="s">
+        <v>96</v>
+      </c>
       <c r="I34" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" t="s">
         <v>147</v>
       </c>
-      <c r="K34">
+      <c r="J34">
         <v>6</v>
       </c>
+      <c r="N34">
+        <v>6</v>
+      </c>
       <c r="O34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q34">
         <v>2</v>
@@ -3451,16 +3419,13 @@
         <v>2</v>
       </c>
       <c r="S34">
-        <v>2</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34" t="s">
+        <v>0</v>
+      </c>
+      <c r="T34" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -3479,17 +3444,20 @@
       <c r="F35" t="s">
         <v>42</v>
       </c>
-      <c r="J35" t="s">
+      <c r="I35" t="s">
         <v>140</v>
       </c>
-      <c r="K35">
+      <c r="J35">
+        <v>12</v>
+      </c>
+      <c r="N35">
         <v>12</v>
       </c>
       <c r="O35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -3498,13 +3466,10 @@
         <v>4</v>
       </c>
       <c r="S35">
-        <v>4</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -3523,20 +3488,23 @@
       <c r="G36">
         <v>29</v>
       </c>
+      <c r="H36" t="s">
+        <v>102</v>
+      </c>
       <c r="I36" t="s">
-        <v>102</v>
-      </c>
-      <c r="J36" t="s">
         <v>103</v>
       </c>
-      <c r="K36">
+      <c r="J36">
         <v>22</v>
       </c>
+      <c r="N36">
+        <v>21</v>
+      </c>
       <c r="O36">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>7</v>
@@ -3545,13 +3513,10 @@
         <v>7</v>
       </c>
       <c r="S36">
-        <v>7</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -3570,20 +3535,23 @@
       <c r="G37">
         <v>6</v>
       </c>
+      <c r="H37" t="s">
+        <v>268</v>
+      </c>
       <c r="I37" t="s">
-        <v>268</v>
-      </c>
-      <c r="J37" t="s">
         <v>105</v>
       </c>
-      <c r="K37">
+      <c r="J37">
         <v>30</v>
       </c>
+      <c r="N37">
+        <v>30</v>
+      </c>
       <c r="O37">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -3592,13 +3560,10 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>10</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -3614,17 +3579,20 @@
       <c r="E38" t="s">
         <v>106</v>
       </c>
-      <c r="J38" t="s">
+      <c r="I38" t="s">
         <v>147</v>
       </c>
-      <c r="K38">
+      <c r="J38">
         <v>6</v>
       </c>
+      <c r="N38">
+        <v>6</v>
+      </c>
       <c r="O38">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q38">
         <v>2</v>
@@ -3633,16 +3601,13 @@
         <v>2</v>
       </c>
       <c r="S38">
-        <v>2</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38" t="s">
+        <v>0</v>
+      </c>
+      <c r="T38" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -3658,17 +3623,20 @@
       <c r="E39" t="s">
         <v>9</v>
       </c>
-      <c r="J39" t="s">
+      <c r="I39" t="s">
         <v>147</v>
       </c>
-      <c r="K39">
+      <c r="J39">
         <v>6</v>
       </c>
+      <c r="N39">
+        <v>6</v>
+      </c>
       <c r="O39">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q39">
         <v>2</v>
@@ -3677,16 +3645,13 @@
         <v>2</v>
       </c>
       <c r="S39">
-        <v>2</v>
-      </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39" t="s">
+        <v>0</v>
+      </c>
+      <c r="T39" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -3705,17 +3670,20 @@
       <c r="F40" t="s">
         <v>84</v>
       </c>
-      <c r="J40" t="s">
+      <c r="I40" t="s">
         <v>155</v>
       </c>
-      <c r="K40">
+      <c r="J40">
         <v>3</v>
       </c>
+      <c r="N40">
+        <v>3</v>
+      </c>
       <c r="O40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40">
         <v>1</v>
@@ -3724,16 +3692,13 @@
         <v>1</v>
       </c>
       <c r="S40">
-        <v>1</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40" t="s">
+        <v>0</v>
+      </c>
+      <c r="T40" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -3752,17 +3717,20 @@
       <c r="F41" t="s">
         <v>107</v>
       </c>
-      <c r="J41" t="s">
+      <c r="I41" t="s">
         <v>271</v>
       </c>
-      <c r="K41">
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="N41">
         <v>1</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -3773,14 +3741,11 @@
       <c r="S41">
         <v>0</v>
       </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41" t="s">
+      <c r="T41" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -3799,17 +3764,20 @@
       <c r="F42" t="s">
         <v>42</v>
       </c>
-      <c r="J42" t="s">
+      <c r="I42" t="s">
         <v>155</v>
       </c>
-      <c r="K42">
+      <c r="J42">
         <v>3</v>
       </c>
+      <c r="N42">
+        <v>3</v>
+      </c>
       <c r="O42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42">
         <v>1</v>
@@ -3818,16 +3786,13 @@
         <v>1</v>
       </c>
       <c r="S42">
-        <v>1</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42" t="s">
+        <v>0</v>
+      </c>
+      <c r="T42" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3846,17 +3811,20 @@
       <c r="F43" t="s">
         <v>15</v>
       </c>
-      <c r="J43" t="s">
+      <c r="I43" t="s">
         <v>155</v>
       </c>
-      <c r="K43">
+      <c r="J43">
         <v>3</v>
       </c>
+      <c r="N43">
+        <v>3</v>
+      </c>
       <c r="O43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43">
         <v>1</v>
@@ -3865,16 +3833,13 @@
         <v>1</v>
       </c>
       <c r="S43">
-        <v>1</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43" t="s">
+        <v>0</v>
+      </c>
+      <c r="T43" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -3893,17 +3858,20 @@
       <c r="F44" t="s">
         <v>29</v>
       </c>
-      <c r="J44" t="s">
+      <c r="I44" t="s">
         <v>155</v>
       </c>
-      <c r="K44">
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="N44">
         <v>0</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44">
         <v>1</v>
@@ -3912,16 +3880,13 @@
         <v>1</v>
       </c>
       <c r="S44">
-        <v>1</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44" t="s">
+        <v>0</v>
+      </c>
+      <c r="T44" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -3940,17 +3905,20 @@
       <c r="F45" t="s">
         <v>15</v>
       </c>
-      <c r="J45" t="s">
+      <c r="I45" t="s">
         <v>155</v>
       </c>
-      <c r="K45">
+      <c r="J45">
         <v>3</v>
       </c>
+      <c r="N45">
+        <v>3</v>
+      </c>
       <c r="O45">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45">
         <v>1</v>
@@ -3959,16 +3927,13 @@
         <v>1</v>
       </c>
       <c r="S45">
-        <v>1</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45" t="s">
+        <v>0</v>
+      </c>
+      <c r="T45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3987,20 +3952,23 @@
       <c r="F46" t="s">
         <v>112</v>
       </c>
+      <c r="H46" t="s">
+        <v>113</v>
+      </c>
       <c r="I46" t="s">
-        <v>113</v>
-      </c>
-      <c r="J46" t="s">
         <v>147</v>
       </c>
-      <c r="K46">
+      <c r="J46">
         <v>6</v>
       </c>
+      <c r="N46">
+        <v>6</v>
+      </c>
       <c r="O46">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q46">
         <v>2</v>
@@ -4009,16 +3977,13 @@
         <v>2</v>
       </c>
       <c r="S46">
-        <v>2</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46" t="s">
+        <v>0</v>
+      </c>
+      <c r="T46" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -4037,20 +4002,23 @@
       <c r="F47" t="s">
         <v>115</v>
       </c>
+      <c r="H47" t="s">
+        <v>116</v>
+      </c>
       <c r="I47" t="s">
-        <v>116</v>
-      </c>
-      <c r="J47" t="s">
         <v>147</v>
       </c>
-      <c r="K47">
+      <c r="J47">
         <v>3</v>
       </c>
+      <c r="N47">
+        <v>3</v>
+      </c>
       <c r="O47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47">
         <v>2</v>
@@ -4059,16 +4027,13 @@
         <v>2</v>
       </c>
       <c r="S47">
-        <v>2</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47" t="s">
+        <v>0</v>
+      </c>
+      <c r="T47" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -4090,20 +4055,23 @@
       <c r="G48">
         <v>8</v>
       </c>
+      <c r="H48" t="s">
+        <v>120</v>
+      </c>
       <c r="I48" t="s">
-        <v>120</v>
-      </c>
-      <c r="J48" t="s">
         <v>122</v>
       </c>
-      <c r="K48">
+      <c r="J48">
         <v>24</v>
       </c>
+      <c r="N48">
+        <v>24</v>
+      </c>
       <c r="O48">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q48">
         <v>8</v>
@@ -4112,13 +4080,10 @@
         <v>8</v>
       </c>
       <c r="S48">
-        <v>8</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -4137,17 +4102,20 @@
       <c r="F49" t="s">
         <v>29</v>
       </c>
-      <c r="J49" t="s">
+      <c r="I49" t="s">
         <v>155</v>
       </c>
-      <c r="K49">
+      <c r="J49">
         <v>3</v>
       </c>
+      <c r="N49">
+        <v>3</v>
+      </c>
       <c r="O49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49">
         <v>1</v>
@@ -4156,13 +4124,10 @@
         <v>1</v>
       </c>
       <c r="S49">
-        <v>1</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -4181,17 +4146,20 @@
       <c r="F50" t="s">
         <v>121</v>
       </c>
-      <c r="J50" t="s">
+      <c r="I50" t="s">
         <v>271</v>
       </c>
-      <c r="K50">
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="N50">
         <v>1</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -4202,11 +4170,8 @@
       <c r="S50">
         <v>0</v>
       </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -4225,37 +4190,36 @@
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4" t="s">
+      <c r="I51" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="K51" s="4">
+      <c r="J51" s="4">
         <v>14</v>
       </c>
+      <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4">
+      <c r="N51" s="4">
         <v>14</v>
       </c>
-      <c r="P51" s="1">
-        <v>0</v>
+      <c r="O51" s="1">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4">
+        <v>7</v>
       </c>
       <c r="Q51" s="4">
         <v>7</v>
       </c>
       <c r="R51" s="4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S51" s="4">
         <v>0</v>
       </c>
-      <c r="T51" s="4">
-        <v>0</v>
-      </c>
-      <c r="U51" s="4"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T51" s="4"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
@@ -4274,37 +4238,36 @@
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4" t="s">
+      <c r="I52" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="K52" s="4">
+      <c r="J52" s="4">
         <v>6</v>
       </c>
+      <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4">
+      <c r="N52" s="4">
         <v>6</v>
       </c>
-      <c r="P52" s="1">
-        <v>0</v>
+      <c r="O52" s="1">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4">
+        <v>3</v>
       </c>
       <c r="Q52" s="4">
         <v>3</v>
       </c>
       <c r="R52" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S52" s="4">
         <v>0</v>
       </c>
-      <c r="T52" s="4">
-        <v>0</v>
-      </c>
-      <c r="U52" s="4"/>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T52" s="4"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>11</v>
       </c>
@@ -4323,37 +4286,36 @@
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4" t="s">
+      <c r="I53" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="K53" s="4">
+      <c r="J53" s="4">
         <v>6</v>
       </c>
+      <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4">
+      <c r="N53" s="4">
         <v>6</v>
       </c>
-      <c r="P53" s="1">
-        <v>0</v>
+      <c r="O53" s="1">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4">
+        <v>3</v>
       </c>
       <c r="Q53" s="4">
         <v>3</v>
       </c>
       <c r="R53" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S53" s="4">
         <v>0</v>
       </c>
-      <c r="T53" s="4">
-        <v>0</v>
-      </c>
-      <c r="U53" s="4"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T53" s="4"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>11</v>
       </c>
@@ -4372,21 +4334,23 @@
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K54" s="1">
-        <v>1</v>
-      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
+      <c r="N54" s="1">
+        <v>1</v>
+      </c>
       <c r="O54" s="1">
         <v>1</v>
       </c>
       <c r="P54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="1">
         <v>0</v>
@@ -4397,12 +4361,9 @@
       <c r="S54" s="1">
         <v>0</v>
       </c>
-      <c r="T54" s="1">
-        <v>0</v>
-      </c>
-      <c r="U54" s="1"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T54" s="1"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>11</v>
       </c>
@@ -4420,24 +4381,26 @@
         <v>143</v>
       </c>
       <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="I55" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J55" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K55" s="1">
-        <v>12</v>
-      </c>
+      <c r="J55" s="1">
+        <v>12</v>
+      </c>
+      <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
+      <c r="N55" s="1">
+        <v>12</v>
+      </c>
       <c r="O55" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q55" s="1">
         <v>4</v>
@@ -4446,14 +4409,11 @@
         <v>4</v>
       </c>
       <c r="S55" s="1">
-        <v>4</v>
-      </c>
-      <c r="T55" s="1">
-        <v>0</v>
-      </c>
-      <c r="U55" s="1"/>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>11</v>
       </c>
@@ -4471,24 +4431,26 @@
         <v>145</v>
       </c>
       <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
+      <c r="H56" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="I56" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J56" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K56" s="1">
+      <c r="J56" s="1">
         <v>6</v>
       </c>
+      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
+      <c r="N56" s="1">
+        <v>6</v>
+      </c>
       <c r="O56" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P56" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="1">
         <v>2</v>
@@ -4497,14 +4459,11 @@
         <v>2</v>
       </c>
       <c r="S56" s="1">
-        <v>2</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1"/>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>11</v>
       </c>
@@ -4522,24 +4481,26 @@
         <v>148</v>
       </c>
       <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
+      <c r="H57" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="I57" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J57" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="K57" s="1">
-        <v>2</v>
-      </c>
+      <c r="J57" s="1">
+        <v>2</v>
+      </c>
+      <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
+      <c r="N57" s="1">
+        <v>2</v>
+      </c>
       <c r="O57" s="1">
         <v>2</v>
       </c>
       <c r="P57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="1">
         <v>0</v>
@@ -4550,12 +4511,9 @@
       <c r="S57" s="1">
         <v>0</v>
       </c>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T57" s="1"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>11</v>
       </c>
@@ -4573,42 +4531,41 @@
         <v>150</v>
       </c>
       <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
+      <c r="H58" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="I58" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J58" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K58" s="1">
-        <v>12</v>
-      </c>
+      <c r="J58" s="1">
+        <v>12</v>
+      </c>
+      <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
+      <c r="N58" s="1">
+        <v>14</v>
+      </c>
       <c r="O58" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P58" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q58" s="1">
         <v>5</v>
       </c>
       <c r="R58" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S58" s="1">
-        <v>4</v>
-      </c>
-      <c r="T58" s="1">
-        <v>0</v>
-      </c>
-      <c r="U58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T58" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>11</v>
       </c>
@@ -4626,24 +4583,26 @@
         <v>153</v>
       </c>
       <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
+      <c r="H59" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="I59" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J59" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K59" s="1">
+      <c r="J59" s="1">
         <v>3</v>
       </c>
+      <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
+      <c r="N59" s="1">
+        <v>3</v>
+      </c>
       <c r="O59" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="1">
         <v>1</v>
@@ -4652,14 +4611,11 @@
         <v>1</v>
       </c>
       <c r="S59" s="1">
-        <v>1</v>
-      </c>
-      <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T59" s="1"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>11</v>
       </c>
@@ -4677,24 +4633,26 @@
         <v>156</v>
       </c>
       <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+      <c r="H60" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I60" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J60" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K60" s="1">
-        <v>1</v>
-      </c>
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
+      <c r="N60" s="1">
+        <v>1</v>
+      </c>
       <c r="O60" s="1">
         <v>1</v>
       </c>
       <c r="P60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="1">
         <v>0</v>
@@ -4705,12 +4663,9 @@
       <c r="S60" s="1">
         <v>0</v>
       </c>
-      <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T60" s="1"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>11</v>
       </c>
@@ -4728,24 +4683,26 @@
         <v>159</v>
       </c>
       <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
+      <c r="H61" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="I61" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J61" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K61" s="1">
+      <c r="J61" s="1">
         <v>3</v>
       </c>
+      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
+      <c r="N61" s="1">
+        <v>3</v>
+      </c>
       <c r="O61" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="1">
         <v>1</v>
@@ -4754,14 +4711,11 @@
         <v>1</v>
       </c>
       <c r="S61" s="1">
-        <v>1</v>
-      </c>
-      <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1"/>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T61" s="1"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>11</v>
       </c>
@@ -4779,19 +4733,21 @@
         <v>161</v>
       </c>
       <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
+      <c r="H62" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="I62" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K62" s="1">
+      <c r="J62" s="1">
         <v>3</v>
       </c>
+      <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
       <c r="O62" s="1">
         <v>0</v>
       </c>
@@ -4807,14 +4763,11 @@
       <c r="S62" s="1">
         <v>0</v>
       </c>
-      <c r="T62" s="1">
-        <v>0</v>
-      </c>
-      <c r="U62" s="1" t="s">
+      <c r="T62" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>11</v>
       </c>
@@ -4832,24 +4785,26 @@
         <v>163</v>
       </c>
       <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
+      <c r="H63" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="I63" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K63" s="1">
-        <v>12</v>
-      </c>
+      <c r="J63" s="1">
+        <v>12</v>
+      </c>
+      <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
+      <c r="N63" s="1">
+        <v>12</v>
+      </c>
       <c r="O63" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P63" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q63" s="1">
         <v>4</v>
@@ -4858,14 +4813,11 @@
         <v>4</v>
       </c>
       <c r="S63" s="1">
-        <v>4</v>
-      </c>
-      <c r="T63" s="1">
-        <v>0</v>
-      </c>
-      <c r="U63" s="1"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T63" s="1"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>11</v>
       </c>
@@ -4883,24 +4835,26 @@
         <v>166</v>
       </c>
       <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
+      <c r="H64" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="I64" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J64" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K64" s="1">
+      <c r="J64" s="1">
         <v>3</v>
       </c>
+      <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
+      <c r="N64" s="1">
+        <v>3</v>
+      </c>
       <c r="O64" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="1">
         <v>1</v>
@@ -4909,14 +4863,11 @@
         <v>1</v>
       </c>
       <c r="S64" s="1">
-        <v>1</v>
-      </c>
-      <c r="T64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="1"/>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T64" s="1"/>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>11</v>
       </c>
@@ -4934,24 +4885,26 @@
         <v>167</v>
       </c>
       <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
+      <c r="H65" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="I65" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J65" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K65" s="1">
+      <c r="J65" s="1">
         <v>9</v>
       </c>
+      <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
+      <c r="N65" s="1">
+        <v>9</v>
+      </c>
       <c r="O65" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P65" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q65" s="1">
         <v>3</v>
@@ -4960,14 +4913,11 @@
         <v>3</v>
       </c>
       <c r="S65" s="1">
-        <v>3</v>
-      </c>
-      <c r="T65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="1"/>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>11</v>
       </c>
@@ -4985,42 +4935,41 @@
         <v>138</v>
       </c>
       <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
+      <c r="H66" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="I66" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J66" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K66" s="1">
+      <c r="J66" s="1">
         <v>4</v>
       </c>
+      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
+      <c r="N66" s="1">
+        <v>4</v>
+      </c>
       <c r="O66" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P66" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q66" s="1">
         <v>2</v>
       </c>
       <c r="R66" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S66" s="1">
         <v>0</v>
       </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
-      <c r="U66" s="1" t="s">
+      <c r="T66" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
         <v>11</v>
       </c>
@@ -5038,19 +4987,21 @@
         <v>29</v>
       </c>
       <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
+      <c r="H67" s="1" t="s">
+        <v>174</v>
+      </c>
       <c r="I67" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="J67" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K67" s="1">
-        <v>1</v>
-      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
       <c r="O67" s="1">
         <v>0</v>
       </c>
@@ -5066,14 +5017,11 @@
       <c r="S67" s="1">
         <v>0</v>
       </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1" t="s">
+      <c r="T67" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>11</v>
       </c>
@@ -5091,42 +5039,41 @@
         <v>175</v>
       </c>
       <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
+      <c r="H68" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="I68" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J68" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K68" s="1">
+      <c r="J68" s="1">
         <v>8</v>
       </c>
+      <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
+      <c r="N68" s="1">
+        <v>8</v>
+      </c>
       <c r="O68" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q68" s="1">
         <v>4</v>
       </c>
       <c r="R68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S68" s="1">
         <v>0</v>
       </c>
-      <c r="T68" s="1">
-        <v>0</v>
-      </c>
-      <c r="U68" s="1" t="s">
+      <c r="T68" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>11</v>
       </c>
@@ -5144,24 +5091,26 @@
         <v>179</v>
       </c>
       <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
+      <c r="H69" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="I69" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J69" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K69" s="1">
-        <v>12</v>
-      </c>
+      <c r="J69" s="1">
+        <v>12</v>
+      </c>
+      <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
+      <c r="N69" s="1">
+        <v>12</v>
+      </c>
       <c r="O69" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P69" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q69" s="1">
         <v>4</v>
@@ -5170,14 +5119,11 @@
         <v>4</v>
       </c>
       <c r="S69" s="1">
-        <v>4</v>
-      </c>
-      <c r="T69" s="1">
-        <v>0</v>
-      </c>
-      <c r="U69" s="1"/>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T69" s="1"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
         <v>11</v>
       </c>
@@ -5195,24 +5141,26 @@
         <v>180</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
+      <c r="H70" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="I70" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J70" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K70" s="1">
-        <v>12</v>
-      </c>
+      <c r="J70" s="1">
+        <v>12</v>
+      </c>
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
+      <c r="N70" s="1">
+        <v>12</v>
+      </c>
       <c r="O70" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q70" s="1">
         <v>4</v>
@@ -5221,14 +5169,11 @@
         <v>4</v>
       </c>
       <c r="S70" s="1">
-        <v>4</v>
-      </c>
-      <c r="T70" s="1">
-        <v>0</v>
-      </c>
-      <c r="U70" s="1"/>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
         <v>11</v>
       </c>
@@ -5246,24 +5191,26 @@
         <v>182</v>
       </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
+      <c r="H71" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="I71" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="J71" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K71" s="1">
+      <c r="J71" s="1">
         <v>6</v>
       </c>
+      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
+      <c r="N71" s="1">
+        <v>6</v>
+      </c>
       <c r="O71" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P71" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q71" s="1">
         <v>2</v>
@@ -5272,14 +5219,11 @@
         <v>2</v>
       </c>
       <c r="S71" s="1">
-        <v>2</v>
-      </c>
-      <c r="T71" s="1">
-        <v>0</v>
-      </c>
-      <c r="U71" s="1"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T71" s="1"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>11</v>
       </c>
@@ -5297,42 +5241,41 @@
         <v>184</v>
       </c>
       <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
+      <c r="H72" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="I72" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J72" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K72" s="1">
+      <c r="J72" s="1">
         <v>3</v>
       </c>
+      <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
+      <c r="N72" s="1">
+        <v>4</v>
+      </c>
       <c r="O72" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P72" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" s="1">
         <v>1</v>
       </c>
       <c r="S72" s="1">
-        <v>1</v>
-      </c>
-      <c r="T72" s="1">
-        <v>0</v>
-      </c>
-      <c r="U72" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T72" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>11</v>
       </c>
@@ -5350,24 +5293,26 @@
         <v>186</v>
       </c>
       <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
+      <c r="H73" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="I73" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J73" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K73" s="1">
+      <c r="J73" s="1">
         <v>3</v>
       </c>
+      <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
+      <c r="N73" s="1">
+        <v>3</v>
+      </c>
       <c r="O73" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="1">
         <v>1</v>
@@ -5376,14 +5321,11 @@
         <v>1</v>
       </c>
       <c r="S73" s="1">
-        <v>1</v>
-      </c>
-      <c r="T73" s="1">
-        <v>0</v>
-      </c>
-      <c r="U73" s="1"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T73" s="1"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
@@ -5401,40 +5343,39 @@
         <v>187</v>
       </c>
       <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
+      <c r="H74" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="I74" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J74" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="K74" s="1">
-        <v>2</v>
-      </c>
+      <c r="J74" s="1">
+        <v>2</v>
+      </c>
+      <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
+      <c r="N74" s="1">
+        <v>2</v>
+      </c>
       <c r="O74" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="1">
         <v>1</v>
       </c>
       <c r="R74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" s="1">
         <v>0</v>
       </c>
-      <c r="T74" s="1">
-        <v>0</v>
-      </c>
-      <c r="U74" s="1"/>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T74" s="1"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>11</v>
       </c>
@@ -5452,42 +5393,41 @@
         <v>190</v>
       </c>
       <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
+      <c r="H75" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="I75" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J75" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="K75" s="1">
+      <c r="J75" s="1">
         <v>9</v>
       </c>
+      <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
+      <c r="N75" s="1">
+        <v>7</v>
+      </c>
       <c r="O75" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P75" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q75" s="1">
         <v>3</v>
       </c>
       <c r="R75" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S75" s="1">
-        <v>1</v>
-      </c>
-      <c r="T75" s="1">
-        <v>0</v>
-      </c>
-      <c r="U75" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T75" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
         <v>11</v>
       </c>
@@ -5505,24 +5445,26 @@
         <v>192</v>
       </c>
       <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
+      <c r="H76" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="I76" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J76" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K76" s="1">
+      <c r="J76" s="1">
         <v>3</v>
       </c>
+      <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
+      <c r="N76" s="1">
+        <v>3</v>
+      </c>
       <c r="O76" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P76" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" s="1">
         <v>1</v>
@@ -5531,14 +5473,11 @@
         <v>1</v>
       </c>
       <c r="S76" s="1">
-        <v>1</v>
-      </c>
-      <c r="T76" s="1">
-        <v>0</v>
-      </c>
-      <c r="U76" s="1"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T76" s="1"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
         <v>11</v>
       </c>
@@ -5556,24 +5495,26 @@
         <v>193</v>
       </c>
       <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
+      <c r="H77" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="I77" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J77" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K77" s="1">
+      <c r="J77" s="1">
         <v>3</v>
       </c>
+      <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
-      <c r="N77" s="1"/>
+      <c r="N77" s="1">
+        <v>3</v>
+      </c>
       <c r="O77" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="1">
         <v>1</v>
@@ -5582,14 +5523,11 @@
         <v>1</v>
       </c>
       <c r="S77" s="1">
-        <v>1</v>
-      </c>
-      <c r="T77" s="1">
-        <v>0</v>
-      </c>
-      <c r="U77" s="1"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T77" s="1"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>11</v>
       </c>
@@ -5607,42 +5545,41 @@
         <v>148</v>
       </c>
       <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
+      <c r="H78" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="I78" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J78" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K78" s="1">
+      <c r="J78" s="1">
         <v>10</v>
       </c>
+      <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
+      <c r="N78" s="1">
+        <v>10</v>
+      </c>
       <c r="O78" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P78" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q78" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R78" s="1">
         <v>3</v>
       </c>
       <c r="S78" s="1">
-        <v>3</v>
-      </c>
-      <c r="T78" s="1">
-        <v>0</v>
-      </c>
-      <c r="U78" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T78" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>11</v>
       </c>
@@ -5663,19 +5600,21 @@
       </c>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" t="s">
+      <c r="I79" t="s">
         <v>155</v>
       </c>
+      <c r="J79" s="4"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
+      <c r="N79" s="4">
+        <v>1</v>
+      </c>
       <c r="O79" s="4">
         <v>1</v>
       </c>
       <c r="P79" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="4">
         <v>0</v>
@@ -5686,12 +5625,9 @@
       <c r="S79" s="4">
         <v>0</v>
       </c>
-      <c r="T79" s="4">
-        <v>0</v>
-      </c>
-      <c r="U79" s="4"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T79" s="4"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
         <v>11</v>
       </c>
@@ -5712,19 +5648,21 @@
       </c>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" t="s">
+      <c r="I80" t="s">
         <v>274</v>
       </c>
+      <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
+      <c r="N80" s="4">
+        <v>9</v>
+      </c>
       <c r="O80" s="4">
         <v>9</v>
       </c>
       <c r="P80" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="4">
         <v>0</v>
@@ -5735,12 +5673,9 @@
       <c r="S80" s="4">
         <v>0</v>
       </c>
-      <c r="T80" s="4">
-        <v>0</v>
-      </c>
-      <c r="U80" s="4"/>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T80" s="4"/>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>11</v>
       </c>
@@ -5761,16 +5696,18 @@
       </c>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" t="s">
+      <c r="I81" t="s">
         <v>252</v>
       </c>
+      <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
+      <c r="N81" s="4">
+        <v>2</v>
+      </c>
       <c r="O81" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P81" s="4">
         <v>0</v>
@@ -5784,12 +5721,9 @@
       <c r="S81" s="4">
         <v>0</v>
       </c>
-      <c r="T81" s="4">
-        <v>0</v>
-      </c>
-      <c r="U81" s="4"/>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T81" s="4"/>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>11</v>
       </c>
@@ -5810,19 +5744,21 @@
       </c>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" t="s">
+      <c r="I82" t="s">
         <v>253</v>
       </c>
+      <c r="J82" s="4"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
+      <c r="N82" s="4">
+        <v>1</v>
+      </c>
       <c r="O82" s="4">
         <v>1</v>
       </c>
       <c r="P82" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="4">
         <v>0</v>
@@ -5833,12 +5769,9 @@
       <c r="S82" s="4">
         <v>0</v>
       </c>
-      <c r="T82" s="4">
-        <v>0</v>
-      </c>
-      <c r="U82" s="4"/>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T82" s="4"/>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>11</v>
       </c>
@@ -5859,19 +5792,21 @@
       </c>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" t="s">
+      <c r="I83" t="s">
         <v>275</v>
       </c>
+      <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
+      <c r="N83" s="4">
+        <v>6</v>
+      </c>
       <c r="O83" s="4">
         <v>6</v>
       </c>
       <c r="P83" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="4">
         <v>0</v>
@@ -5882,12 +5817,9 @@
       <c r="S83" s="4">
         <v>0</v>
       </c>
-      <c r="T83" s="4">
-        <v>0</v>
-      </c>
-      <c r="U83" s="4"/>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T83" s="4"/>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
         <v>11</v>
       </c>
@@ -5908,19 +5840,21 @@
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" t="s">
+      <c r="I84" t="s">
         <v>155</v>
       </c>
+      <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
+      <c r="N84" s="4">
+        <v>3</v>
+      </c>
       <c r="O84" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P84" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="4">
         <v>1</v>
@@ -5929,14 +5863,11 @@
         <v>1</v>
       </c>
       <c r="S84" s="4">
-        <v>1</v>
-      </c>
-      <c r="T84" s="4">
-        <v>0</v>
-      </c>
-      <c r="U84" s="4"/>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T84" s="4"/>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>11</v>
       </c>
@@ -5957,19 +5888,21 @@
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" t="s">
+      <c r="I85" t="s">
         <v>252</v>
       </c>
+      <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
+      <c r="N85" s="4">
+        <v>2</v>
+      </c>
       <c r="O85" s="4">
         <v>2</v>
       </c>
       <c r="P85" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="4">
         <v>0</v>
@@ -5980,12 +5913,9 @@
       <c r="S85" s="4">
         <v>0</v>
       </c>
-      <c r="T85" s="4">
-        <v>0</v>
-      </c>
-      <c r="U85" s="4"/>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T85" s="4"/>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>11</v>
       </c>
@@ -6006,19 +5936,21 @@
       </c>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" t="s">
+      <c r="I86" t="s">
         <v>274</v>
       </c>
+      <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
+      <c r="N86" s="4">
+        <v>9</v>
+      </c>
       <c r="O86" s="4">
         <v>9</v>
       </c>
       <c r="P86" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="4">
         <v>0</v>
@@ -6029,12 +5961,9 @@
       <c r="S86" s="4">
         <v>0</v>
       </c>
-      <c r="T86" s="4">
-        <v>0</v>
-      </c>
-      <c r="U86" s="4"/>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T86" s="4"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
         <v>11</v>
       </c>
@@ -6055,19 +5984,21 @@
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" t="s">
+      <c r="I87" t="s">
         <v>155</v>
       </c>
+      <c r="J87" s="4"/>
       <c r="K87" s="4"/>
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
+      <c r="N87" s="4">
+        <v>3</v>
+      </c>
       <c r="O87" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P87" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="4">
         <v>1</v>
@@ -6076,14 +6007,11 @@
         <v>1</v>
       </c>
       <c r="S87" s="4">
-        <v>1</v>
-      </c>
-      <c r="T87" s="4">
-        <v>0</v>
-      </c>
-      <c r="U87" s="4"/>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T87" s="4"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>11</v>
       </c>
@@ -6104,19 +6032,21 @@
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" t="s">
+      <c r="I88" t="s">
         <v>155</v>
       </c>
+      <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
+      <c r="N88" s="4">
+        <v>3</v>
+      </c>
       <c r="O88" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P88" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="4">
         <v>1</v>
@@ -6125,14 +6055,11 @@
         <v>1</v>
       </c>
       <c r="S88" s="4">
-        <v>1</v>
-      </c>
-      <c r="T88" s="4">
-        <v>0</v>
-      </c>
-      <c r="U88" s="4"/>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T88" s="4"/>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>11</v>
       </c>
@@ -6153,19 +6080,21 @@
       </c>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" t="s">
+      <c r="I89" t="s">
         <v>252</v>
       </c>
+      <c r="J89" s="4"/>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
+      <c r="N89" s="4">
+        <v>2</v>
+      </c>
       <c r="O89" s="4">
         <v>2</v>
       </c>
       <c r="P89" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="4">
         <v>0</v>
@@ -6176,12 +6105,9 @@
       <c r="S89" s="4">
         <v>0</v>
       </c>
-      <c r="T89" s="4">
-        <v>0</v>
-      </c>
-      <c r="U89" s="4"/>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T89" s="4"/>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
         <v>11</v>
       </c>
@@ -6202,19 +6128,21 @@
       </c>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" t="s">
+      <c r="I90" t="s">
         <v>252</v>
       </c>
+      <c r="J90" s="4"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
+      <c r="N90" s="4">
+        <v>2</v>
+      </c>
       <c r="O90" s="4">
         <v>2</v>
       </c>
       <c r="P90" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="4">
         <v>0</v>
@@ -6225,12 +6153,9 @@
       <c r="S90" s="4">
         <v>0</v>
       </c>
-      <c r="T90" s="4">
-        <v>0</v>
-      </c>
-      <c r="U90" s="4"/>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T90" s="4"/>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>11</v>
       </c>
@@ -6251,19 +6176,21 @@
       </c>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" t="s">
+      <c r="I91" t="s">
         <v>252</v>
       </c>
+      <c r="J91" s="4"/>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
+      <c r="N91" s="4">
+        <v>2</v>
+      </c>
       <c r="O91" s="4">
         <v>2</v>
       </c>
       <c r="P91" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="4">
         <v>0</v>
@@ -6274,12 +6201,9 @@
       <c r="S91" s="4">
         <v>0</v>
       </c>
-      <c r="T91" s="4">
-        <v>0</v>
-      </c>
-      <c r="U91" s="4"/>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T91" s="4"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>11</v>
       </c>
@@ -6300,19 +6224,21 @@
       </c>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" t="s">
+      <c r="I92" t="s">
         <v>253</v>
       </c>
+      <c r="J92" s="4"/>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
+      <c r="N92" s="4">
+        <v>1</v>
+      </c>
       <c r="O92" s="4">
         <v>1</v>
       </c>
       <c r="P92" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="4">
         <v>0</v>
@@ -6323,12 +6249,9 @@
       <c r="S92" s="4">
         <v>0</v>
       </c>
-      <c r="T92" s="4">
-        <v>0</v>
-      </c>
-      <c r="U92" s="4"/>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T92" s="4"/>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
         <v>11</v>
       </c>
@@ -6349,19 +6272,21 @@
       </c>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" t="s">
+      <c r="I93" t="s">
         <v>275</v>
       </c>
+      <c r="J93" s="4"/>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
+      <c r="N93" s="4">
+        <v>6</v>
+      </c>
       <c r="O93" s="4">
         <v>6</v>
       </c>
       <c r="P93" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="4">
         <v>0</v>
@@ -6372,12 +6297,9 @@
       <c r="S93" s="4">
         <v>0</v>
       </c>
-      <c r="T93" s="4">
-        <v>0</v>
-      </c>
-      <c r="U93" s="4"/>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T93" s="4"/>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>11</v>
       </c>
@@ -6398,19 +6320,21 @@
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" t="s">
+      <c r="I94" t="s">
         <v>253</v>
       </c>
+      <c r="J94" s="4"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
+      <c r="N94" s="4">
+        <v>1</v>
+      </c>
       <c r="O94" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" s="4">
         <v>1</v>
@@ -6419,14 +6343,11 @@
         <v>1</v>
       </c>
       <c r="S94" s="4">
-        <v>1</v>
-      </c>
-      <c r="T94" s="4">
-        <v>0</v>
-      </c>
-      <c r="U94" s="4"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T94" s="4"/>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>11</v>
       </c>
@@ -6447,19 +6368,21 @@
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" t="s">
+      <c r="I95" t="s">
         <v>253</v>
       </c>
+      <c r="J95" s="4"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
+      <c r="N95" s="4">
+        <v>1</v>
+      </c>
       <c r="O95" s="4">
         <v>1</v>
       </c>
       <c r="P95" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="4">
         <v>0</v>
@@ -6470,12 +6393,9 @@
       <c r="S95" s="4">
         <v>0</v>
       </c>
-      <c r="T95" s="4">
-        <v>0</v>
-      </c>
-      <c r="U95" s="4"/>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T95" s="4"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
         <v>11</v>
       </c>
@@ -6496,19 +6416,21 @@
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" t="s">
+      <c r="I96" t="s">
         <v>272</v>
       </c>
+      <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
+      <c r="N96" s="4">
+        <v>5</v>
+      </c>
       <c r="O96" s="4">
         <v>5</v>
       </c>
       <c r="P96" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="4">
         <v>0</v>
@@ -6519,12 +6441,9 @@
       <c r="S96" s="4">
         <v>0</v>
       </c>
-      <c r="T96" s="4">
-        <v>0</v>
-      </c>
-      <c r="U96" s="4"/>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T96" s="4"/>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>11</v>
       </c>
@@ -6545,19 +6464,21 @@
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" t="s">
+      <c r="I97" t="s">
         <v>155</v>
       </c>
+      <c r="J97" s="4"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
+      <c r="N97" s="4">
+        <v>3</v>
+      </c>
       <c r="O97" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P97" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="4">
         <v>1</v>
@@ -6566,14 +6487,11 @@
         <v>1</v>
       </c>
       <c r="S97" s="4">
-        <v>1</v>
-      </c>
-      <c r="T97" s="4">
-        <v>0</v>
-      </c>
-      <c r="U97" s="4"/>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T97" s="4"/>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>11</v>
       </c>
@@ -6594,19 +6512,21 @@
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" t="s">
+      <c r="I98" t="s">
         <v>252</v>
       </c>
+      <c r="J98" s="4"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
+      <c r="N98" s="4">
+        <v>2</v>
+      </c>
       <c r="O98" s="4">
         <v>2</v>
       </c>
       <c r="P98" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q98" s="4">
         <v>0</v>
@@ -6617,12 +6537,9 @@
       <c r="S98" s="4">
         <v>0</v>
       </c>
-      <c r="T98" s="4">
-        <v>0</v>
-      </c>
-      <c r="U98" s="4"/>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T98" s="4"/>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
         <v>11</v>
       </c>
@@ -6643,19 +6560,21 @@
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" t="s">
+      <c r="I99" t="s">
         <v>275</v>
       </c>
+      <c r="J99" s="4"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
+      <c r="N99" s="4">
+        <v>6</v>
+      </c>
       <c r="O99" s="4">
         <v>6</v>
       </c>
       <c r="P99" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="4">
         <v>0</v>
@@ -6666,12 +6585,9 @@
       <c r="S99" s="4">
         <v>0</v>
       </c>
-      <c r="T99" s="4">
-        <v>0</v>
-      </c>
-      <c r="U99" s="4"/>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T99" s="4"/>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>11</v>
       </c>
@@ -6692,19 +6608,21 @@
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" t="s">
+      <c r="I100" t="s">
         <v>155</v>
       </c>
+      <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
+      <c r="N100" s="4">
+        <v>3</v>
+      </c>
       <c r="O100" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P100" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" s="4">
         <v>1</v>
@@ -6713,14 +6631,11 @@
         <v>1</v>
       </c>
       <c r="S100" s="4">
-        <v>1</v>
-      </c>
-      <c r="T100" s="4">
-        <v>0</v>
-      </c>
-      <c r="U100" s="4"/>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T100" s="4"/>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>11</v>
       </c>
@@ -6741,19 +6656,21 @@
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" t="s">
+      <c r="I101" t="s">
         <v>253</v>
       </c>
+      <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
+      <c r="N101" s="4">
+        <v>1</v>
+      </c>
       <c r="O101" s="4">
         <v>1</v>
       </c>
       <c r="P101" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="4">
         <v>0</v>
@@ -6764,12 +6681,9 @@
       <c r="S101" s="4">
         <v>0</v>
       </c>
-      <c r="T101" s="4">
-        <v>0</v>
-      </c>
-      <c r="U101" s="4"/>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T101" s="4"/>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
         <v>11</v>
       </c>
@@ -6790,19 +6704,21 @@
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" t="s">
+      <c r="I102" t="s">
         <v>253</v>
       </c>
+      <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
-      <c r="N102" s="1"/>
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
       <c r="O102" s="1">
         <v>1</v>
       </c>
       <c r="P102" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="1">
         <v>0</v>
@@ -6813,12 +6729,9 @@
       <c r="S102" s="1">
         <v>0</v>
       </c>
-      <c r="T102" s="1">
-        <v>0</v>
-      </c>
-      <c r="U102" s="1"/>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T102" s="1"/>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>11</v>
       </c>
@@ -6839,36 +6752,35 @@
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="4" t="s">
+      <c r="I103" s="4" t="s">
         <v>263</v>
       </c>
+      <c r="J103" s="4"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
-      <c r="N103" s="4"/>
-      <c r="O103" s="4">
+      <c r="N103" s="4">
         <f>TFO!J23</f>
         <v>62</v>
       </c>
+      <c r="O103" s="4">
+        <v>0</v>
+      </c>
       <c r="P103" s="4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q103" s="4">
         <v>21</v>
       </c>
       <c r="R103" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S103" s="4">
-        <v>20</v>
-      </c>
-      <c r="T103" s="4">
-        <v>0</v>
-      </c>
-      <c r="U103" s="4"/>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T103" s="4"/>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>11</v>
       </c>
@@ -6889,36 +6801,35 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4" t="s">
+      <c r="I104" s="4" t="s">
         <v>264</v>
       </c>
+      <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
+      <c r="N104" s="4">
+        <f>TFO!J24</f>
+        <v>2</v>
+      </c>
       <c r="O104" s="4">
-        <f>TFO!J24</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P104" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="4">
         <v>1</v>
       </c>
       <c r="R104" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S104" s="4">
         <v>0</v>
       </c>
-      <c r="T104" s="4">
-        <v>0</v>
-      </c>
-      <c r="U104" s="4"/>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T104" s="4"/>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>11</v>
       </c>
@@ -6939,20 +6850,22 @@
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4" t="s">
+      <c r="I105" s="4" t="s">
         <v>265</v>
       </c>
+      <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
-      <c r="N105" s="4"/>
-      <c r="O105" s="4">
+      <c r="N105" s="4">
         <f>TFO!J25</f>
         <v>33</v>
       </c>
+      <c r="O105" s="4">
+        <v>0</v>
+      </c>
       <c r="P105" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q105" s="4">
         <v>12</v>
@@ -6961,14 +6874,11 @@
         <v>12</v>
       </c>
       <c r="S105" s="4">
-        <v>12</v>
-      </c>
-      <c r="T105" s="4">
-        <v>0</v>
-      </c>
-      <c r="U105" s="4"/>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T105" s="4"/>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>11</v>
       </c>
@@ -6989,20 +6899,22 @@
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4" t="s">
+      <c r="I106" s="4" t="s">
         <v>266</v>
       </c>
+      <c r="J106" s="4"/>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4">
+      <c r="N106" s="4">
         <f>TFO!J26</f>
         <v>51</v>
       </c>
+      <c r="O106" s="4">
+        <v>0</v>
+      </c>
       <c r="P106" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q106" s="4">
         <v>17</v>
@@ -7011,14 +6923,11 @@
         <v>17</v>
       </c>
       <c r="S106" s="4">
-        <v>17</v>
-      </c>
-      <c r="T106" s="4">
-        <v>0</v>
-      </c>
-      <c r="U106" s="4"/>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T106" s="4"/>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>11</v>
       </c>
@@ -7039,20 +6948,22 @@
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" t="s">
+      <c r="I107" t="s">
         <v>147</v>
       </c>
+      <c r="J107" s="4"/>
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
-      <c r="O107" s="4">
+      <c r="N107" s="4">
         <f>TFO!J27</f>
         <v>6</v>
       </c>
+      <c r="O107" s="4">
+        <v>0</v>
+      </c>
       <c r="P107" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q107" s="4">
         <v>2</v>
@@ -7061,14 +6972,11 @@
         <v>2</v>
       </c>
       <c r="S107" s="4">
-        <v>2</v>
-      </c>
-      <c r="T107" s="4">
-        <v>0</v>
-      </c>
-      <c r="U107" s="4"/>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T107" s="4"/>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
         <v>11</v>
       </c>
@@ -7089,20 +6997,22 @@
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" t="s">
+      <c r="I108" t="s">
         <v>147</v>
       </c>
+      <c r="J108" s="4"/>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4">
+      <c r="N108" s="4">
         <f>TFO!J28</f>
         <v>6</v>
       </c>
+      <c r="O108" s="4">
+        <v>0</v>
+      </c>
       <c r="P108" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="4">
         <v>2</v>
@@ -7111,14 +7021,11 @@
         <v>2</v>
       </c>
       <c r="S108" s="4">
-        <v>2</v>
-      </c>
-      <c r="T108" s="4">
-        <v>0</v>
-      </c>
-      <c r="U108" s="4"/>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T108" s="4"/>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>11</v>
       </c>
@@ -7139,20 +7046,22 @@
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" t="s">
+      <c r="I109" t="s">
         <v>155</v>
       </c>
+      <c r="J109" s="4"/>
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4">
+      <c r="N109" s="4">
         <f>TFO!J29</f>
         <v>3</v>
       </c>
+      <c r="O109" s="4">
+        <v>0</v>
+      </c>
       <c r="P109" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="4">
         <v>1</v>
@@ -7161,14 +7070,11 @@
         <v>1</v>
       </c>
       <c r="S109" s="4">
-        <v>1</v>
-      </c>
-      <c r="T109" s="4">
-        <v>0</v>
-      </c>
-      <c r="U109" s="4"/>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T109" s="4"/>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>11</v>
       </c>
@@ -7189,20 +7095,22 @@
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" t="s">
+      <c r="I110" t="s">
         <v>155</v>
       </c>
+      <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
-      <c r="N110" s="4"/>
-      <c r="O110" s="4">
+      <c r="N110" s="4">
         <f>TFO!J30</f>
         <v>3</v>
       </c>
+      <c r="O110" s="4">
+        <v>0</v>
+      </c>
       <c r="P110" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" s="4">
         <v>1</v>
@@ -7211,14 +7119,11 @@
         <v>1</v>
       </c>
       <c r="S110" s="4">
-        <v>1</v>
-      </c>
-      <c r="T110" s="4">
-        <v>0</v>
-      </c>
-      <c r="U110" s="4"/>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T110" s="4"/>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
         <v>11</v>
       </c>
@@ -7239,20 +7144,22 @@
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" t="s">
+      <c r="I111" t="s">
         <v>147</v>
       </c>
+      <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
-      <c r="N111" s="4"/>
-      <c r="O111" s="4">
+      <c r="N111" s="4">
         <f>TFO!J31</f>
         <v>6</v>
       </c>
+      <c r="O111" s="4">
+        <v>0</v>
+      </c>
       <c r="P111" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q111" s="4">
         <v>2</v>
@@ -7261,14 +7168,11 @@
         <v>2</v>
       </c>
       <c r="S111" s="4">
-        <v>2</v>
-      </c>
-      <c r="T111" s="4">
-        <v>0</v>
-      </c>
-      <c r="U111" s="4"/>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T111" s="4"/>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>11</v>
       </c>
@@ -7287,20 +7191,22 @@
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" t="s">
+      <c r="I112" t="s">
         <v>155</v>
       </c>
+      <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
-      <c r="N112" s="4"/>
-      <c r="O112" s="4">
+      <c r="N112" s="4">
         <f>TFO!J32</f>
         <v>3</v>
       </c>
+      <c r="O112" s="4">
+        <v>0</v>
+      </c>
       <c r="P112" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="4">
         <v>1</v>
@@ -7309,14 +7215,11 @@
         <v>1</v>
       </c>
       <c r="S112" s="4">
-        <v>1</v>
-      </c>
-      <c r="T112" s="4">
-        <v>0</v>
-      </c>
-      <c r="U112" s="4"/>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T112" s="4"/>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>11</v>
       </c>
@@ -7335,20 +7238,22 @@
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" t="s">
+      <c r="I113" t="s">
         <v>253</v>
       </c>
+      <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
-      <c r="N113" s="4"/>
+      <c r="N113" s="4">
+        <f>TFO!J33</f>
+        <v>1</v>
+      </c>
       <c r="O113" s="4">
-        <f>TFO!J33</f>
         <v>1</v>
       </c>
       <c r="P113" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="4">
         <v>0</v>
@@ -7359,12 +7264,9 @@
       <c r="S113" s="4">
         <v>0</v>
       </c>
-      <c r="T113" s="4">
-        <v>0</v>
-      </c>
-      <c r="U113" s="4"/>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T113" s="4"/>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
         <v>11</v>
       </c>
@@ -7383,20 +7285,22 @@
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-      <c r="J114" t="s">
+      <c r="I114" t="s">
         <v>140</v>
       </c>
+      <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
-      <c r="N114" s="4"/>
+      <c r="N114" s="4">
+        <f>TFO!J34</f>
+        <v>12</v>
+      </c>
       <c r="O114" s="4">
-        <f>TFO!J34</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P114" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q114" s="4">
         <v>4</v>
@@ -7405,14 +7309,11 @@
         <v>4</v>
       </c>
       <c r="S114" s="4">
-        <v>4</v>
-      </c>
-      <c r="T114" s="4">
-        <v>0</v>
-      </c>
-      <c r="U114" s="4"/>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="T114" s="4"/>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>11</v>
       </c>
@@ -7433,16 +7334,18 @@
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
-      <c r="I115" s="4"/>
-      <c r="J115" t="s">
+      <c r="I115" t="s">
         <v>271</v>
       </c>
+      <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
-      <c r="N115" s="4"/>
+      <c r="N115" s="4">
+        <f>TFO!J35</f>
+        <v>0</v>
+      </c>
       <c r="O115" s="4">
-        <f>TFO!J35</f>
         <v>0</v>
       </c>
       <c r="P115" s="4">
@@ -7457,12 +7360,9 @@
       <c r="S115" s="4">
         <v>0</v>
       </c>
-      <c r="T115" s="4">
-        <v>0</v>
-      </c>
-      <c r="U115" s="4"/>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T115" s="4"/>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>11</v>
       </c>
@@ -7483,20 +7383,22 @@
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
-      <c r="J116" t="s">
+      <c r="I116" t="s">
         <v>253</v>
       </c>
+      <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
-      <c r="N116" s="4"/>
+      <c r="N116" s="4">
+        <f>TFO!J36</f>
+        <v>1</v>
+      </c>
       <c r="O116" s="4">
-        <f>TFO!J36</f>
         <v>1</v>
       </c>
       <c r="P116" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q116" s="4">
         <v>0</v>
@@ -7507,12 +7409,9 @@
       <c r="S116" s="4">
         <v>0</v>
       </c>
-      <c r="T116" s="4">
-        <v>0</v>
-      </c>
-      <c r="U116" s="4"/>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="T116" s="4"/>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
         <v>11</v>
       </c>
@@ -7533,20 +7432,22 @@
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
-      <c r="J117" t="s">
+      <c r="I117" t="s">
         <v>147</v>
       </c>
+      <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
-      <c r="N117" s="4"/>
-      <c r="O117" s="4">
+      <c r="N117" s="4">
         <f>TFO!J37</f>
         <v>6</v>
       </c>
+      <c r="O117" s="4">
+        <v>0</v>
+      </c>
       <c r="P117" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q117" s="4">
         <v>2</v>
@@ -7555,12 +7456,9 @@
         <v>2</v>
       </c>
       <c r="S117" s="4">
-        <v>2</v>
-      </c>
-      <c r="T117" s="4">
-        <v>0</v>
-      </c>
-      <c r="U117" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="T117" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
